--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -5780,7 +5780,7 @@
         </is>
       </c>
       <c r="I6" s="115" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"소형승용","Small Passenger"),"중형승용","Medium Passenger"),"대형승용","HEAVY Passenger"),"중형승합","Medium Ven"),"대형승합","Large Ven"),"중형화물","Medium Cargo")</f>
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
         <v>0</v>
       </c>
     </row>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="377">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -326,11 +326,6 @@
   <si>
     <r>
       <t xml:space="preserve">NAME</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">VIA AUTO</t>
     </r>
   </si>
   <si>
@@ -6135,12 +6130,9 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="118" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">VIA AUTO</t>
-          </r>
-        </is>
+      <c r="D14" s="118" t="str">
+        <f>B14</f>
+        <v>0</v>
       </c>
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
@@ -6827,7 +6819,7 @@
       <c r="C7" s="255"/>
       <c r="D7" s="256"/>
       <c r="E7" s="258" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" s="255"/>
       <c r="G7" s="255"/>
@@ -6860,7 +6852,7 @@
       </c>
       <c r="D8" s="255"/>
       <c r="E8" s="260" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" s="255"/>
       <c r="G8" s="255"/>
@@ -8454,7 +8446,7 @@
       <c r="C7" s="255"/>
       <c r="D7" s="256"/>
       <c r="E7" s="258" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F7" s="255"/>
       <c r="G7" s="255"/>
@@ -8487,7 +8479,7 @@
       </c>
       <c r="D8" s="255"/>
       <c r="E8" s="260" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F8" s="255"/>
       <c r="G8" s="255"/>
@@ -10341,7 +10333,7 @@
       </c>
       <c r="D21" s="304"/>
       <c r="E21" s="324" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F21" s="251"/>
       <c r="G21" s="304"/>
@@ -11250,7 +11242,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A3" s="346" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="263"/>
       <c r="E3" s="229" t="inlineStr">
@@ -12268,7 +12260,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A3" s="346" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D3" s="263"/>
       <c r="E3" s="229" t="inlineStr">
@@ -13269,7 +13261,7 @@
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="246" customFormat="1">
       <c r="A2" s="244" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D2" s="244"/>
     </row>
@@ -13457,7 +13449,7 @@
       </c>
       <c r="B16" s="388"/>
       <c r="C16" s="389" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D16" s="388"/>
       <c r="E16" s="240" t="inlineStr">
@@ -13468,7 +13460,7 @@
         </is>
       </c>
       <c r="F16" s="390" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G16" s="388"/>
     </row>
@@ -13482,7 +13474,7 @@
       </c>
       <c r="B17" s="388"/>
       <c r="C17" s="389" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D17" s="388"/>
       <c r="E17" s="240" t="inlineStr">
@@ -13493,7 +13485,7 @@
         </is>
       </c>
       <c r="F17" s="241" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G17" s="388"/>
     </row>
@@ -13507,7 +13499,7 @@
       </c>
       <c r="B18" s="388"/>
       <c r="C18" s="389" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D18" s="388"/>
       <c r="E18" s="240" t="inlineStr">
@@ -13518,7 +13510,7 @@
         </is>
       </c>
       <c r="F18" s="391" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G18" s="388"/>
     </row>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -10011,8 +10011,12 @@
         </is>
       </c>
       <c r="D9" s="305"/>
-      <c r="E9" s="306"/>
-      <c r="G9" s="305"/>
+      <c r="E9" s="185" t="str">
+        <f>구매리스트!D4</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="185"/>
+      <c r="G9" s="185"/>
       <c r="H9" s="181" t="inlineStr">
         <is>
           <r>
@@ -11076,7 +11080,6 @@
     <mergeCell ref="H22:J22"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="A5:O5"/>
-    <mergeCell ref="E8:G9"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="K33:N33"/>
     <mergeCell ref="A49:J49"/>
@@ -11153,6 +11156,8 @@
     <mergeCell ref="K50:O51"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="H25:J25"/>
+    <mergeCell ref="E8:G8"/>
+    <mergeCell ref="E9:G9"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true" horizontalCentered="true"/>
   <pageMargins left="0.31496062992126" right="0.23622047244094" top="0.45" bottom="0.51181102362205" header="0.31496062992126" footer="0.31496062992126"/>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="378">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -207,6 +207,9 @@
     <r>
       <t xml:space="preserve">5</t>
     </r>
+  </si>
+  <si>
+    <t>최대적재량</t>
   </si>
   <si>
     <r>
@@ -3473,7 +3476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="397">
+  <cellXfs count="399">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4428,9 +4431,6 @@
     <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="33" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="37" numFmtId="0" fillId="11" borderId="47" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
-    </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="48" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4663,6 +4663,15 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="6" borderId="64" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="37" numFmtId="0" fillId="0" borderId="29" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
@@ -5891,12 +5900,8 @@
           </r>
         </is>
       </c>
-      <c r="H9" s="103" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
+      <c r="H9" s="103" t="s">
+        <v>36</v>
       </c>
       <c r="I9" s="101" t="inlineStr">
         <is>
@@ -6819,7 +6824,7 @@
       <c r="C7" s="255"/>
       <c r="D7" s="256"/>
       <c r="E7" s="258" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F7" s="255"/>
       <c r="G7" s="255"/>
@@ -6852,7 +6857,7 @@
       </c>
       <c r="D8" s="255"/>
       <c r="E8" s="260" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F8" s="255"/>
       <c r="G8" s="255"/>
@@ -7360,7 +7365,8 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="11" t="str">
+        <f>구매리스트!I9</f>
         <v>0</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -8446,7 +8452,7 @@
       <c r="C7" s="255"/>
       <c r="D7" s="256"/>
       <c r="E7" s="258" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F7" s="255"/>
       <c r="G7" s="255"/>
@@ -8479,7 +8485,7 @@
       </c>
       <c r="D8" s="255"/>
       <c r="E8" s="260" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F8" s="255"/>
       <c r="G8" s="255"/>
@@ -8989,7 +8995,8 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="120">
+      <c r="I23" s="398" t="str">
+        <f>구매리스트!I9</f>
         <v>0</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
@@ -10170,12 +10177,9 @@
       </c>
       <c r="I14" s="316"/>
       <c r="J14" s="314"/>
-      <c r="K14" s="318" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">자가용</t>
-          </r>
-        </is>
+      <c r="K14" s="310" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="L14" s="316"/>
       <c r="M14" s="316"/>
@@ -10207,18 +10211,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="319"/>
-      <c r="E16" s="320"/>
-      <c r="F16" s="321"/>
-      <c r="G16" s="319"/>
-      <c r="H16" s="320"/>
-      <c r="I16" s="321"/>
-      <c r="J16" s="319"/>
-      <c r="K16" s="320"/>
-      <c r="L16" s="321"/>
-      <c r="M16" s="321"/>
-      <c r="N16" s="321"/>
-      <c r="O16" s="321"/>
+      <c r="D16" s="318"/>
+      <c r="E16" s="319"/>
+      <c r="F16" s="320"/>
+      <c r="G16" s="318"/>
+      <c r="H16" s="319"/>
+      <c r="I16" s="320"/>
+      <c r="J16" s="318"/>
+      <c r="K16" s="319"/>
+      <c r="L16" s="320"/>
+      <c r="M16" s="320"/>
+      <c r="N16" s="320"/>
+      <c r="O16" s="320"/>
     </row>
     <row r="17" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
       <c r="B17" s="305"/>
@@ -10275,7 +10279,7 @@
     </row>
     <row r="19" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A19" s="253"/>
-      <c r="B19" s="322"/>
+      <c r="B19" s="321"/>
       <c r="C19" s="183" t="inlineStr">
         <is>
           <r>
@@ -10283,10 +10287,10 @@
           </r>
         </is>
       </c>
-      <c r="D19" s="322"/>
-      <c r="E19" s="323"/>
+      <c r="D19" s="321"/>
+      <c r="E19" s="322"/>
       <c r="F19" s="253"/>
-      <c r="G19" s="322"/>
+      <c r="G19" s="321"/>
       <c r="H19" s="183" t="inlineStr">
         <is>
           <r>
@@ -10295,8 +10299,8 @@
         </is>
       </c>
       <c r="I19" s="253"/>
-      <c r="J19" s="322"/>
-      <c r="K19" s="323"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="322"/>
       <c r="L19" s="253"/>
       <c r="M19" s="253"/>
       <c r="N19" s="253"/>
@@ -10336,8 +10340,8 @@
         </is>
       </c>
       <c r="D21" s="304"/>
-      <c r="E21" s="324" t="s">
-        <v>256</v>
+      <c r="E21" s="396" t="s">
+        <v>257</v>
       </c>
       <c r="F21" s="251"/>
       <c r="G21" s="304"/>
@@ -10350,7 +10354,7 @@
       </c>
       <c r="I21" s="251"/>
       <c r="J21" s="304"/>
-      <c r="K21" s="324" t="inlineStr">
+      <c r="K21" s="323" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">120111-0922270</t>
@@ -10370,7 +10374,7 @@
           </r>
         </is>
       </c>
-      <c r="B22" s="322"/>
+      <c r="B22" s="321"/>
       <c r="C22" s="183" t="inlineStr">
         <is>
           <r>
@@ -10378,10 +10382,10 @@
           </r>
         </is>
       </c>
-      <c r="D22" s="322"/>
-      <c r="E22" s="323"/>
+      <c r="D22" s="321"/>
+      <c r="E22" s="322"/>
       <c r="F22" s="253"/>
-      <c r="G22" s="322"/>
+      <c r="G22" s="321"/>
       <c r="H22" s="187" t="inlineStr">
         <is>
           <r>
@@ -10391,12 +10395,12 @@
         </is>
       </c>
       <c r="I22" s="253"/>
-      <c r="J22" s="322"/>
-      <c r="K22" s="323"/>
+      <c r="J22" s="321"/>
+      <c r="K22" s="322"/>
       <c r="L22" s="253"/>
       <c r="M22" s="253"/>
       <c r="N22" s="253"/>
-      <c r="O22" s="322"/>
+      <c r="O22" s="321"/>
     </row>
     <row r="23" spans="1:15" customHeight="1" ht="11.25" s="246" customFormat="1">
       <c r="A23" s="84"/>
@@ -10426,7 +10430,7 @@
       <c r="B24" s="251"/>
       <c r="C24" s="251"/>
       <c r="D24" s="304"/>
-      <c r="E24" s="325" t="str">
+      <c r="E24" s="324" t="str">
         <f>구매리스트!B7</f>
         <v>0</v>
       </c>
@@ -10441,7 +10445,7 @@
       </c>
       <c r="I24" s="251"/>
       <c r="J24" s="304"/>
-      <c r="K24" s="326" t="inlineStr">
+      <c r="K24" s="325" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">증명용</t>
@@ -10461,12 +10465,12 @@
           </r>
         </is>
       </c>
-      <c r="B25" s="327"/>
-      <c r="C25" s="327"/>
-      <c r="D25" s="328"/>
-      <c r="E25" s="329"/>
-      <c r="F25" s="327"/>
-      <c r="G25" s="328"/>
+      <c r="B25" s="326"/>
+      <c r="C25" s="326"/>
+      <c r="D25" s="327"/>
+      <c r="E25" s="328"/>
+      <c r="F25" s="326"/>
+      <c r="G25" s="327"/>
       <c r="H25" s="216" t="inlineStr">
         <is>
           <r>
@@ -10474,13 +10478,13 @@
           </r>
         </is>
       </c>
-      <c r="I25" s="327"/>
-      <c r="J25" s="328"/>
-      <c r="K25" s="329"/>
-      <c r="L25" s="327"/>
-      <c r="M25" s="327"/>
-      <c r="N25" s="327"/>
-      <c r="O25" s="328"/>
+      <c r="I25" s="326"/>
+      <c r="J25" s="327"/>
+      <c r="K25" s="328"/>
+      <c r="L25" s="326"/>
+      <c r="M25" s="326"/>
+      <c r="N25" s="326"/>
+      <c r="O25" s="327"/>
     </row>
     <row r="26" spans="1:15" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A26" s="214" t="inlineStr">
@@ -10543,10 +10547,10 @@
       </c>
       <c r="B27" s="253"/>
       <c r="C27" s="253"/>
-      <c r="D27" s="322"/>
-      <c r="E27" s="323"/>
+      <c r="D27" s="321"/>
+      <c r="E27" s="322"/>
       <c r="F27" s="253"/>
-      <c r="G27" s="322"/>
+      <c r="G27" s="321"/>
       <c r="H27" s="183" t="inlineStr">
         <is>
           <r>
@@ -10555,7 +10559,7 @@
         </is>
       </c>
       <c r="I27" s="253"/>
-      <c r="J27" s="322"/>
+      <c r="J27" s="321"/>
       <c r="K27" s="98" t="inlineStr">
         <is>
           <r>
@@ -10733,20 +10737,20 @@
           </r>
         </is>
       </c>
-      <c r="B38" s="330"/>
-      <c r="C38" s="330"/>
-      <c r="D38" s="330"/>
-      <c r="E38" s="330"/>
-      <c r="F38" s="330"/>
-      <c r="G38" s="330"/>
-      <c r="H38" s="330"/>
-      <c r="I38" s="330"/>
-      <c r="J38" s="330"/>
-      <c r="K38" s="330"/>
-      <c r="L38" s="330"/>
-      <c r="M38" s="330"/>
-      <c r="N38" s="330"/>
-      <c r="O38" s="330"/>
+      <c r="B38" s="329"/>
+      <c r="C38" s="329"/>
+      <c r="D38" s="329"/>
+      <c r="E38" s="329"/>
+      <c r="F38" s="329"/>
+      <c r="G38" s="329"/>
+      <c r="H38" s="329"/>
+      <c r="I38" s="329"/>
+      <c r="J38" s="329"/>
+      <c r="K38" s="329"/>
+      <c r="L38" s="329"/>
+      <c r="M38" s="329"/>
+      <c r="N38" s="329"/>
+      <c r="O38" s="329"/>
     </row>
     <row r="39" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A39" s="221" t="inlineStr">
@@ -10756,20 +10760,20 @@
           </r>
         </is>
       </c>
-      <c r="B39" s="331"/>
-      <c r="C39" s="331"/>
-      <c r="D39" s="331"/>
-      <c r="E39" s="331"/>
-      <c r="F39" s="331"/>
-      <c r="G39" s="331"/>
-      <c r="H39" s="331"/>
-      <c r="I39" s="331"/>
-      <c r="J39" s="331"/>
-      <c r="K39" s="331"/>
-      <c r="L39" s="331"/>
-      <c r="M39" s="331"/>
-      <c r="N39" s="331"/>
-      <c r="O39" s="331"/>
+      <c r="B39" s="330"/>
+      <c r="C39" s="330"/>
+      <c r="D39" s="330"/>
+      <c r="E39" s="330"/>
+      <c r="F39" s="330"/>
+      <c r="G39" s="330"/>
+      <c r="H39" s="330"/>
+      <c r="I39" s="330"/>
+      <c r="J39" s="330"/>
+      <c r="K39" s="330"/>
+      <c r="L39" s="330"/>
+      <c r="M39" s="330"/>
+      <c r="N39" s="330"/>
+      <c r="O39" s="330"/>
     </row>
     <row r="40" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A40" s="192" t="inlineStr">
@@ -10806,15 +10810,15 @@
           </r>
         </is>
       </c>
-      <c r="B43" s="332"/>
-      <c r="C43" s="332"/>
-      <c r="D43" s="332"/>
-      <c r="E43" s="332"/>
-      <c r="F43" s="332"/>
-      <c r="G43" s="332"/>
-      <c r="H43" s="332"/>
-      <c r="I43" s="332"/>
-      <c r="J43" s="333"/>
+      <c r="B43" s="331"/>
+      <c r="C43" s="331"/>
+      <c r="D43" s="331"/>
+      <c r="E43" s="331"/>
+      <c r="F43" s="331"/>
+      <c r="G43" s="331"/>
+      <c r="H43" s="331"/>
+      <c r="I43" s="331"/>
+      <c r="J43" s="332"/>
       <c r="K43" s="223" t="inlineStr">
         <is>
           <r>
@@ -10822,10 +10826,10 @@
           </r>
         </is>
       </c>
-      <c r="L43" s="332"/>
-      <c r="M43" s="332"/>
-      <c r="N43" s="332"/>
-      <c r="O43" s="333"/>
+      <c r="L43" s="331"/>
+      <c r="M43" s="331"/>
+      <c r="N43" s="331"/>
+      <c r="O43" s="332"/>
     </row>
     <row r="44" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A44" s="76" t="inlineStr">
@@ -10854,7 +10858,7 @@
       <c r="L44" s="309"/>
       <c r="M44" s="309"/>
       <c r="N44" s="309"/>
-      <c r="O44" s="334"/>
+      <c r="O44" s="333"/>
     </row>
     <row r="45" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A45" s="76" t="inlineStr">
@@ -10873,8 +10877,8 @@
       <c r="H45" s="76"/>
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
-      <c r="K45" s="335"/>
-      <c r="O45" s="336"/>
+      <c r="K45" s="334"/>
+      <c r="O45" s="335"/>
     </row>
     <row r="46" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A46" s="224" t="inlineStr">
@@ -10884,8 +10888,8 @@
           </r>
         </is>
       </c>
-      <c r="K46" s="335"/>
-      <c r="O46" s="336"/>
+      <c r="K46" s="334"/>
+      <c r="O46" s="335"/>
     </row>
     <row r="47" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A47" s="192" t="inlineStr">
@@ -10895,8 +10899,8 @@
           </r>
         </is>
       </c>
-      <c r="K47" s="335"/>
-      <c r="O47" s="336"/>
+      <c r="K47" s="334"/>
+      <c r="O47" s="335"/>
     </row>
     <row r="48" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A48" s="192" t="inlineStr">
@@ -10906,8 +10910,8 @@
           </r>
         </is>
       </c>
-      <c r="K48" s="335"/>
-      <c r="O48" s="336"/>
+      <c r="K48" s="334"/>
+      <c r="O48" s="335"/>
     </row>
     <row r="49" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A49" s="192" t="inlineStr">
@@ -10918,8 +10922,8 @@
         </is>
       </c>
       <c r="B49" s="246"/>
-      <c r="K49" s="335"/>
-      <c r="O49" s="336"/>
+      <c r="K49" s="334"/>
+      <c r="O49" s="335"/>
     </row>
     <row r="50" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A50" s="196" t="inlineStr">
@@ -10938,7 +10942,7 @@
       <c r="H50" s="309"/>
       <c r="I50" s="309"/>
       <c r="J50" s="309"/>
-      <c r="K50" s="337" t="inlineStr">
+      <c r="K50" s="336" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">말소등록일부터 6개월 이내</t>
@@ -10948,7 +10952,7 @@
       <c r="L50" s="309"/>
       <c r="M50" s="309"/>
       <c r="N50" s="309"/>
-      <c r="O50" s="334"/>
+      <c r="O50" s="333"/>
     </row>
     <row r="51" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A51" s="193" t="inlineStr">
@@ -10967,11 +10971,11 @@
       <c r="H51" s="313"/>
       <c r="I51" s="313"/>
       <c r="J51" s="313"/>
-      <c r="K51" s="338"/>
+      <c r="K51" s="337"/>
       <c r="L51" s="313"/>
       <c r="M51" s="313"/>
       <c r="N51" s="313"/>
-      <c r="O51" s="339"/>
+      <c r="O51" s="338"/>
     </row>
     <row r="52" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A52" s="194" t="inlineStr">
@@ -10981,15 +10985,15 @@
           </r>
         </is>
       </c>
-      <c r="B52" s="340"/>
-      <c r="C52" s="340"/>
-      <c r="D52" s="340"/>
-      <c r="E52" s="340"/>
-      <c r="F52" s="340"/>
-      <c r="G52" s="340"/>
-      <c r="H52" s="340"/>
-      <c r="I52" s="340"/>
-      <c r="J52" s="340"/>
+      <c r="B52" s="339"/>
+      <c r="C52" s="339"/>
+      <c r="D52" s="339"/>
+      <c r="E52" s="339"/>
+      <c r="F52" s="339"/>
+      <c r="G52" s="339"/>
+      <c r="H52" s="339"/>
+      <c r="I52" s="339"/>
+      <c r="J52" s="339"/>
       <c r="K52" s="195" t="inlineStr">
         <is>
           <r>
@@ -10997,10 +11001,10 @@
           </r>
         </is>
       </c>
-      <c r="L52" s="340"/>
-      <c r="M52" s="340"/>
-      <c r="N52" s="340"/>
-      <c r="O52" s="341"/>
+      <c r="L52" s="339"/>
+      <c r="M52" s="339"/>
+      <c r="N52" s="339"/>
+      <c r="O52" s="340"/>
     </row>
     <row r="53" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A53" s="190" t="inlineStr">
@@ -11018,7 +11022,7 @@
       <c r="G53" s="253"/>
       <c r="H53" s="253"/>
       <c r="I53" s="253"/>
-      <c r="J53" s="342"/>
+      <c r="J53" s="341"/>
       <c r="K53" s="189" t="inlineStr">
         <is>
           <r>
@@ -11197,7 +11201,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="47.25" s="246" customFormat="1">
-      <c r="A1" s="343" t="inlineStr">
+      <c r="A1" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL INVOICE</t>
@@ -11214,7 +11218,7 @@
       <c r="I1" s="256"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A2" s="344" t="inlineStr">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
@@ -11236,7 +11240,7 @@
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
-      <c r="H2" s="345" t="inlineStr">
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
@@ -11246,8 +11250,8 @@
       <c r="I2" s="252"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A3" s="346" t="s">
-        <v>308</v>
+      <c r="A3" s="345" t="s">
+        <v>309</v>
       </c>
       <c r="D3" s="263"/>
       <c r="E3" s="229" t="inlineStr">
@@ -11267,7 +11271,7 @@
     <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A4" s="272"/>
       <c r="D4" s="263"/>
-      <c r="E4" s="347" t="inlineStr">
+      <c r="E4" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
@@ -11285,7 +11289,7 @@
     <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A6" s="272"/>
       <c r="D6" s="263"/>
-      <c r="E6" s="348" t="inlineStr">
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
@@ -11299,7 +11303,7 @@
       <c r="B7" s="253"/>
       <c r="C7" s="253"/>
       <c r="D7" s="254"/>
-      <c r="E7" s="348" t="inlineStr">
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
@@ -11309,7 +11313,7 @@
       <c r="I7" s="263"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A8" s="344" t="inlineStr">
+      <c r="A8" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
@@ -11319,7 +11323,7 @@
       <c r="B8" s="251"/>
       <c r="C8" s="251"/>
       <c r="D8" s="252"/>
-      <c r="E8" s="349" t="inlineStr">
+      <c r="E8" s="348" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
@@ -11332,7 +11336,7 @@
       <c r="I8" s="254"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
-      <c r="A9" s="350" t="str">
+      <c r="A9" s="349" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
@@ -11386,7 +11390,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A12" s="344" t="inlineStr">
+      <c r="A12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
@@ -11396,7 +11400,7 @@
       <c r="B12" s="251"/>
       <c r="C12" s="251"/>
       <c r="D12" s="252"/>
-      <c r="E12" s="344" t="inlineStr">
+      <c r="E12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
@@ -11409,7 +11413,7 @@
       <c r="I12" s="252"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A13" s="351" t="inlineStr">
+      <c r="A13" s="350" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
@@ -11438,7 +11442,7 @@
       <c r="I14" s="254"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A15" s="344" t="inlineStr">
+      <c r="A15" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
@@ -11472,12 +11476,12 @@
         <v>0</v>
       </c>
       <c r="B16" s="253"/>
-      <c r="C16" s="352" t="str">
+      <c r="C16" s="351" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
       <c r="D16" s="254"/>
-      <c r="E16" s="353" t="inlineStr">
+      <c r="E16" s="352" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11487,7 +11491,7 @@
       <c r="I16" s="263"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A17" s="344" t="inlineStr">
+      <c r="A17" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
@@ -11503,7 +11507,7 @@
         </is>
       </c>
       <c r="D17" s="252"/>
-      <c r="E17" s="354" t="str">
+      <c r="E17" s="353" t="str">
         <f>구매리스트!D12</f>
         <v>0</v>
       </c>
@@ -11513,12 +11517,12 @@
       <c r="I17" s="252"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A18" s="352" t="str">
+      <c r="A18" s="351" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
       <c r="B18" s="254"/>
-      <c r="C18" s="355" t="str">
+      <c r="C18" s="354" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
@@ -11546,7 +11550,7 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="356" t="inlineStr">
+      <c r="E19" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
@@ -11616,7 +11620,7 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="357" t="inlineStr">
+      <c r="E21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
@@ -11624,21 +11628,21 @@
         </is>
       </c>
       <c r="F21" s="256"/>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="G21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="359" t="inlineStr">
+      <c r="H21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
           </r>
         </is>
       </c>
-      <c r="I21" s="360" t="inlineStr">
+      <c r="I21" s="359" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Shipping</t>
@@ -11648,7 +11652,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A22" s="361">
+      <c r="A22" s="360">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -11663,7 +11667,7 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="362">
+      <c r="E22" s="397">
         <v>1</v>
       </c>
       <c r="F22" s="256"/>
@@ -11685,8 +11689,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A23" s="364"/>
-      <c r="B23" s="365"/>
+      <c r="A23" s="363"/>
+      <c r="B23" s="364"/>
       <c r="C23" s="255"/>
       <c r="D23" s="255"/>
       <c r="E23" s="255"/>
@@ -11694,13 +11698,13 @@
       <c r="G23" s="255"/>
       <c r="H23" s="255"/>
       <c r="I23" s="256"/>
-      <c r="J23" s="363"/>
+      <c r="J23" s="362"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A24" s="364">
+      <c r="A24" s="363">
         <v>2</v>
       </c>
-      <c r="B24" s="366" t="inlineStr">
+      <c r="B24" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11721,9 +11725,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="367"/>
+      <c r="E24" s="366"/>
       <c r="F24" s="256"/>
-      <c r="G24" s="368" t="inlineStr">
+      <c r="G24" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11737,20 +11741,20 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="363">
+      <c r="I24" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="362">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A25" s="364"/>
-      <c r="B25" s="365" t="inlineStr">
+      <c r="A25" s="363"/>
+      <c r="B25" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11764,13 +11768,13 @@
       <c r="G25" s="255"/>
       <c r="H25" s="255"/>
       <c r="I25" s="256"/>
-      <c r="J25" s="363"/>
+      <c r="J25" s="362"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A26" s="364">
+      <c r="A26" s="363">
         <v>3</v>
       </c>
-      <c r="B26" s="366" t="inlineStr">
+      <c r="B26" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11791,9 +11795,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="367"/>
+      <c r="E26" s="366"/>
       <c r="F26" s="256"/>
-      <c r="G26" s="368" t="inlineStr">
+      <c r="G26" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11807,20 +11811,20 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="363">
+      <c r="I26" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="362">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A27" s="364"/>
-      <c r="B27" s="365" t="inlineStr">
+      <c r="A27" s="363"/>
+      <c r="B27" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11834,13 +11838,13 @@
       <c r="G27" s="255"/>
       <c r="H27" s="255"/>
       <c r="I27" s="256"/>
-      <c r="J27" s="363"/>
+      <c r="J27" s="362"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A28" s="364">
+      <c r="A28" s="363">
         <v>4</v>
       </c>
-      <c r="B28" s="370" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11861,9 +11865,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="367"/>
+      <c r="E28" s="366"/>
       <c r="F28" s="256"/>
-      <c r="G28" s="368" t="inlineStr">
+      <c r="G28" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11877,26 +11881,26 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="363">
+      <c r="I28" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="362">
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A29" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="365" t="inlineStr">
+      <c r="A29" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11913,10 +11917,10 @@
       <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A30" s="364">
+      <c r="A30" s="363">
         <v>5</v>
       </c>
-      <c r="B30" s="370" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11937,9 +11941,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="367"/>
+      <c r="E30" s="366"/>
       <c r="F30" s="256"/>
-      <c r="G30" s="368" t="inlineStr">
+      <c r="G30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11953,7 +11957,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="369" t="inlineStr">
+      <c r="I30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11963,14 +11967,14 @@
       <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A31" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="365" t="inlineStr">
+      <c r="A31" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -11995,7 +11999,7 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="371"/>
+      <c r="C32" s="370"/>
       <c r="D32" s="234" t="inlineStr">
         <is>
           <r>
@@ -12003,14 +12007,14 @@
           </r>
         </is>
       </c>
-      <c r="E32" s="371"/>
+      <c r="E32" s="370"/>
       <c r="F32" s="234"/>
       <c r="G32" s="234"/>
       <c r="H32" s="228" t="str">
         <f>SUM(H22:I22,H24:I24,H26:I26,H28:I28,H30:I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="372"/>
+      <c r="I32" s="371"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
@@ -12215,7 +12219,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" customHeight="1" ht="47.25" s="246" customFormat="1">
-      <c r="A1" s="343" t="inlineStr">
+      <c r="A1" s="342" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">COMMERCIAL PACKING LIST</t>
@@ -12232,7 +12236,7 @@
       <c r="I1" s="256"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A2" s="344" t="inlineStr">
+      <c r="A2" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">1) Shipper / Exporter</t>
@@ -12254,7 +12258,7 @@
         <f>차량인보이스!G2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="345" t="inlineStr">
+      <c r="H2" s="344" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">ORIGINAL</t>
@@ -12264,8 +12268,8 @@
       <c r="I2" s="252"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A3" s="346" t="s">
-        <v>308</v>
+      <c r="A3" s="345" t="s">
+        <v>309</v>
       </c>
       <c r="D3" s="263"/>
       <c r="E3" s="229" t="inlineStr">
@@ -12285,7 +12289,7 @@
     <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A4" s="272"/>
       <c r="D4" s="263"/>
-      <c r="E4" s="347" t="inlineStr">
+      <c r="E4" s="346" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">CERTIFICATE OF ORIGIN</t>
@@ -12303,7 +12307,7 @@
     <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A6" s="272"/>
       <c r="D6" s="263"/>
-      <c r="E6" s="348" t="inlineStr">
+      <c r="E6" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Issued by</t>
@@ -12317,7 +12321,7 @@
       <c r="B7" s="253"/>
       <c r="C7" s="253"/>
       <c r="D7" s="254"/>
-      <c r="E7" s="348" t="inlineStr">
+      <c r="E7" s="347" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">THE KOREA CHAMBER OF COMMERCE &amp; INDUSTRY</t>
@@ -12327,7 +12331,7 @@
       <c r="I7" s="263"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A8" s="344" t="inlineStr">
+      <c r="A8" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">2) For account &amp; risk of Messers.</t>
@@ -12337,7 +12341,7 @@
       <c r="B8" s="251"/>
       <c r="C8" s="251"/>
       <c r="D8" s="252"/>
-      <c r="E8" s="349" t="inlineStr">
+      <c r="E8" s="348" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Seoul, Republic of korea</t>
@@ -12350,7 +12354,7 @@
       <c r="I8" s="254"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
-      <c r="A9" s="373" t="str">
+      <c r="A9" s="372" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
@@ -12404,7 +12408,7 @@
       </c>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A12" s="344" t="inlineStr">
+      <c r="A12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">3) Notify party</t>
@@ -12414,7 +12418,7 @@
       <c r="B12" s="251"/>
       <c r="C12" s="251"/>
       <c r="D12" s="252"/>
-      <c r="E12" s="344" t="inlineStr">
+      <c r="E12" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">9) No. &amp; date of L/C</t>
@@ -12427,7 +12431,7 @@
       <c r="I12" s="252"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
-      <c r="A13" s="351" t="inlineStr">
+      <c r="A13" s="350" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">SAME AS ABOVE</t>
@@ -12456,7 +12460,7 @@
       <c r="I14" s="254"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A15" s="344" t="inlineStr">
+      <c r="A15" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">4) Port of loading</t>
@@ -12490,12 +12494,12 @@
         <v>0</v>
       </c>
       <c r="B16" s="253"/>
-      <c r="C16" s="352" t="str">
+      <c r="C16" s="351" t="str">
         <f>구매리스트!D10</f>
         <v>0</v>
       </c>
       <c r="D16" s="254"/>
-      <c r="E16" s="353" t="inlineStr">
+      <c r="E16" s="352" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12505,7 +12509,7 @@
       <c r="I16" s="263"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
-      <c r="A17" s="344" t="inlineStr">
+      <c r="A17" s="343" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">6) Vessel name</t>
@@ -12521,7 +12525,7 @@
         </is>
       </c>
       <c r="D17" s="252"/>
-      <c r="E17" s="354" t="str">
+      <c r="E17" s="353" t="str">
         <f>차량인보이스!E17</f>
         <v>0</v>
       </c>
@@ -12531,12 +12535,12 @@
       <c r="I17" s="252"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
-      <c r="A18" s="352" t="str">
+      <c r="A18" s="351" t="str">
         <f>구매리스트!B11</f>
         <v>0</v>
       </c>
       <c r="B18" s="254"/>
-      <c r="C18" s="355" t="str">
+      <c r="C18" s="354" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
@@ -12564,7 +12568,7 @@
         </is>
       </c>
       <c r="D19" s="26"/>
-      <c r="E19" s="356" t="inlineStr">
+      <c r="E19" s="355" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">13) Quantity</t>
@@ -12634,7 +12638,7 @@
           </r>
         </is>
       </c>
-      <c r="E21" s="357" t="inlineStr">
+      <c r="E21" s="356" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Q'TY</t>
@@ -12642,14 +12646,14 @@
         </is>
       </c>
       <c r="F21" s="256"/>
-      <c r="G21" s="358" t="inlineStr">
+      <c r="G21" s="357" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">Unit Price</t>
           </r>
         </is>
       </c>
-      <c r="H21" s="359" t="inlineStr">
+      <c r="H21" s="358" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">AMOUNT</t>
@@ -12667,7 +12671,7 @@
       <c r="J21" s="18"/>
     </row>
     <row r="22" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A22" s="361">
+      <c r="A22" s="360">
         <v>1</v>
       </c>
       <c r="B22" s="123" t="str">
@@ -12682,19 +12686,19 @@
         <f>차량인보이스!D22</f>
         <v>0</v>
       </c>
-      <c r="E22" s="362" t="str">
+      <c r="E22" s="361" t="str">
         <f>차량인보이스!E22</f>
         <v>0</v>
       </c>
       <c r="F22" s="256"/>
-      <c r="G22" s="374" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="H22" s="374" t="inlineStr">
+      <c r="G22" s="373" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="H22" s="373" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12705,7 +12709,7 @@
         <f>구매리스트!I8</f>
         <v>0</v>
       </c>
-      <c r="J22" s="363" t="inlineStr">
+      <c r="J22" s="362" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12714,8 +12718,8 @@
       </c>
     </row>
     <row r="23" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A23" s="364"/>
-      <c r="B23" s="365"/>
+      <c r="A23" s="363"/>
+      <c r="B23" s="364"/>
       <c r="C23" s="255"/>
       <c r="D23" s="255"/>
       <c r="E23" s="255"/>
@@ -12723,13 +12727,13 @@
       <c r="G23" s="255"/>
       <c r="H23" s="255"/>
       <c r="I23" s="256"/>
-      <c r="J23" s="363"/>
+      <c r="J23" s="362"/>
     </row>
     <row r="24" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A24" s="364">
+      <c r="A24" s="363">
         <v>2</v>
       </c>
-      <c r="B24" s="366" t="inlineStr">
+      <c r="B24" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12750,9 +12754,9 @@
           </r>
         </is>
       </c>
-      <c r="E24" s="367"/>
+      <c r="E24" s="366"/>
       <c r="F24" s="256"/>
-      <c r="G24" s="368" t="inlineStr">
+      <c r="G24" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12766,14 +12770,14 @@
           </r>
         </is>
       </c>
-      <c r="I24" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J24" s="363" t="inlineStr">
+      <c r="I24" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J24" s="362" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12782,8 +12786,8 @@
       </c>
     </row>
     <row r="25" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A25" s="364"/>
-      <c r="B25" s="365" t="inlineStr">
+      <c r="A25" s="363"/>
+      <c r="B25" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12797,13 +12801,13 @@
       <c r="G25" s="255"/>
       <c r="H25" s="255"/>
       <c r="I25" s="256"/>
-      <c r="J25" s="363"/>
+      <c r="J25" s="362"/>
     </row>
     <row r="26" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A26" s="364">
+      <c r="A26" s="363">
         <v>3</v>
       </c>
-      <c r="B26" s="366" t="inlineStr">
+      <c r="B26" s="365" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12824,9 +12828,9 @@
           </r>
         </is>
       </c>
-      <c r="E26" s="367"/>
+      <c r="E26" s="366"/>
       <c r="F26" s="256"/>
-      <c r="G26" s="368" t="inlineStr">
+      <c r="G26" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12840,14 +12844,14 @@
           </r>
         </is>
       </c>
-      <c r="I26" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J26" s="363" t="inlineStr">
+      <c r="I26" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J26" s="362" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12856,8 +12860,8 @@
       </c>
     </row>
     <row r="27" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A27" s="364"/>
-      <c r="B27" s="365" t="inlineStr">
+      <c r="A27" s="363"/>
+      <c r="B27" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12871,13 +12875,13 @@
       <c r="G27" s="255"/>
       <c r="H27" s="255"/>
       <c r="I27" s="256"/>
-      <c r="J27" s="363"/>
+      <c r="J27" s="362"/>
     </row>
     <row r="28" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A28" s="364">
+      <c r="A28" s="363">
         <v>4</v>
       </c>
-      <c r="B28" s="370" t="inlineStr">
+      <c r="B28" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12898,9 +12902,9 @@
           </r>
         </is>
       </c>
-      <c r="E28" s="367"/>
+      <c r="E28" s="366"/>
       <c r="F28" s="256"/>
-      <c r="G28" s="368" t="inlineStr">
+      <c r="G28" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12914,14 +12918,14 @@
           </r>
         </is>
       </c>
-      <c r="I28" s="369" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="J28" s="363" t="inlineStr">
+      <c r="I28" s="368" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="J28" s="362" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12930,14 +12934,14 @@
       </c>
     </row>
     <row r="29" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A29" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B29" s="365" t="inlineStr">
+      <c r="A29" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B29" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12954,10 +12958,10 @@
       <c r="J29" s="18"/>
     </row>
     <row r="30" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
-      <c r="A30" s="364">
+      <c r="A30" s="363">
         <v>5</v>
       </c>
-      <c r="B30" s="370" t="inlineStr">
+      <c r="B30" s="369" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12978,9 +12982,9 @@
           </r>
         </is>
       </c>
-      <c r="E30" s="367"/>
+      <c r="E30" s="366"/>
       <c r="F30" s="256"/>
-      <c r="G30" s="368" t="inlineStr">
+      <c r="G30" s="367" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -12994,7 +12998,7 @@
           </r>
         </is>
       </c>
-      <c r="I30" s="369" t="inlineStr">
+      <c r="I30" s="368" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13004,14 +13008,14 @@
       <c r="J30" s="18"/>
     </row>
     <row r="31" spans="1:10" customHeight="1" ht="36" s="246" customFormat="1">
-      <c r="A31" s="364" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve"> </t>
-          </r>
-        </is>
-      </c>
-      <c r="B31" s="365" t="inlineStr">
+      <c r="A31" s="363" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve"> </t>
+          </r>
+        </is>
+      </c>
+      <c r="B31" s="364" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve"> </t>
@@ -13036,7 +13040,7 @@
           </r>
         </is>
       </c>
-      <c r="C32" s="371"/>
+      <c r="C32" s="370"/>
       <c r="D32" s="236" t="inlineStr">
         <is>
           <r>
@@ -13044,14 +13048,14 @@
           </r>
         </is>
       </c>
-      <c r="E32" s="371"/>
+      <c r="E32" s="370"/>
       <c r="F32" s="236"/>
       <c r="G32" s="236"/>
       <c r="H32" s="237" t="str">
         <f>SUM(I22,I24,I26,I28,I30)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="372"/>
+      <c r="I32" s="371"/>
       <c r="J32" s="18"/>
     </row>
     <row r="33" spans="1:10">
@@ -13266,7 +13270,7 @@
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="246" customFormat="1">
       <c r="A2" s="244" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="D2" s="244"/>
     </row>
@@ -13279,11 +13283,11 @@
           </r>
         </is>
       </c>
-      <c r="F3" s="375" t="str">
+      <c r="F3" s="374" t="str">
         <f>구매리스트!D11</f>
         <v>0</v>
       </c>
-      <c r="G3" s="376"/>
+      <c r="G3" s="375"/>
     </row>
     <row r="4" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A4" s="47"/>
@@ -13297,11 +13301,11 @@
           </r>
         </is>
       </c>
-      <c r="F4" s="377" t="str">
+      <c r="F4" s="376" t="str">
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
-      <c r="G4" s="378"/>
+      <c r="G4" s="377"/>
     </row>
     <row r="5" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A5" s="239"/>
@@ -13313,11 +13317,11 @@
           </r>
         </is>
       </c>
-      <c r="F5" s="379" t="str">
+      <c r="F5" s="378" t="str">
         <f>구매리스트!D14</f>
         <v>0</v>
       </c>
-      <c r="G5" s="378"/>
+      <c r="G5" s="377"/>
     </row>
     <row r="6" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A6" s="239"/>
@@ -13329,8 +13333,8 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="380"/>
-      <c r="G6" s="378"/>
+      <c r="F6" s="379"/>
+      <c r="G6" s="377"/>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A7" s="239"/>
@@ -13341,8 +13345,8 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="381"/>
-      <c r="G7" s="378"/>
+      <c r="F7" s="380"/>
+      <c r="G7" s="377"/>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A8" s="239"/>
@@ -13353,8 +13357,8 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="382"/>
-      <c r="G8" s="378"/>
+      <c r="F8" s="381"/>
+      <c r="G8" s="377"/>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A9" s="239"/>
@@ -13366,8 +13370,8 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="380"/>
-      <c r="G9" s="378"/>
+      <c r="F9" s="379"/>
+      <c r="G9" s="377"/>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A10" s="239"/>
@@ -13385,11 +13389,11 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="383" t="str">
+      <c r="F11" s="382" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G11" s="378"/>
+      <c r="G11" s="377"/>
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A12" s="238"/>
@@ -13400,11 +13404,11 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="383" t="str">
+      <c r="F12" s="382" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
-      <c r="G12" s="378"/>
+      <c r="G12" s="377"/>
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A13" s="245"/>
@@ -13417,32 +13421,32 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="384" t="str">
+      <c r="F13" s="383" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="378"/>
+      <c r="G13" s="377"/>
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="17.25" s="246" customFormat="1">
       <c r="A14" s="245"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="385"/>
+      <c r="E14" s="384"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A15" s="386" t="inlineStr">
+      <c r="A15" s="385" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="387"/>
-      <c r="C15" s="387"/>
-      <c r="D15" s="387"/>
-      <c r="E15" s="387"/>
-      <c r="F15" s="387"/>
-      <c r="G15" s="388"/>
+      <c r="B15" s="386"/>
+      <c r="C15" s="386"/>
+      <c r="D15" s="386"/>
+      <c r="E15" s="386"/>
+      <c r="F15" s="386"/>
+      <c r="G15" s="387"/>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A16" s="240" t="inlineStr">
@@ -13452,11 +13456,11 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="388"/>
-      <c r="C16" s="389" t="s">
-        <v>359</v>
-      </c>
-      <c r="D16" s="388"/>
+      <c r="B16" s="387"/>
+      <c r="C16" s="388" t="s">
+        <v>360</v>
+      </c>
+      <c r="D16" s="387"/>
       <c r="E16" s="240" t="inlineStr">
         <is>
           <r>
@@ -13464,10 +13468,10 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="390" t="s">
-        <v>361</v>
-      </c>
-      <c r="G16" s="388"/>
+      <c r="F16" s="389" t="s">
+        <v>362</v>
+      </c>
+      <c r="G16" s="387"/>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A17" s="240" t="inlineStr">
@@ -13477,11 +13481,11 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="388"/>
-      <c r="C17" s="389" t="s">
-        <v>363</v>
-      </c>
-      <c r="D17" s="388"/>
+      <c r="B17" s="387"/>
+      <c r="C17" s="388" t="s">
+        <v>364</v>
+      </c>
+      <c r="D17" s="387"/>
       <c r="E17" s="240" t="inlineStr">
         <is>
           <r>
@@ -13490,9 +13494,9 @@
         </is>
       </c>
       <c r="F17" s="241" t="s">
-        <v>365</v>
-      </c>
-      <c r="G17" s="388"/>
+        <v>366</v>
+      </c>
+      <c r="G17" s="387"/>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A18" s="240" t="inlineStr">
@@ -13502,11 +13506,11 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="388"/>
-      <c r="C18" s="389" t="s">
-        <v>367</v>
-      </c>
-      <c r="D18" s="388"/>
+      <c r="B18" s="387"/>
+      <c r="C18" s="388" t="s">
+        <v>368</v>
+      </c>
+      <c r="D18" s="387"/>
       <c r="E18" s="240" t="inlineStr">
         <is>
           <r>
@@ -13514,15 +13518,15 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="391" t="s">
-        <v>369</v>
-      </c>
-      <c r="G18" s="388"/>
+      <c r="F18" s="390" t="s">
+        <v>370</v>
+      </c>
+      <c r="G18" s="387"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="385"/>
+      <c r="E19" s="384"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
@@ -13567,7 +13571,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="388"/>
+      <c r="G20" s="387"/>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A21" s="133" t="str">
@@ -13587,11 +13591,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="392" t="str">
+      <c r="F21" s="391" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="388"/>
+      <c r="G21" s="387"/>
     </row>
     <row r="22" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A22" s="41"/>
@@ -13599,8 +13603,8 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="393"/>
-      <c r="G22" s="388"/>
+      <c r="F22" s="392"/>
+      <c r="G22" s="387"/>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A23" s="41"/>
@@ -13608,8 +13612,8 @@
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="393"/>
-      <c r="G23" s="388"/>
+      <c r="F23" s="392"/>
+      <c r="G23" s="387"/>
     </row>
     <row r="24" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A24" s="41"/>
@@ -13617,8 +13621,8 @@
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="393"/>
-      <c r="G24" s="388"/>
+      <c r="F24" s="392"/>
+      <c r="G24" s="387"/>
     </row>
     <row r="25" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A25" s="41"/>
@@ -13626,8 +13630,8 @@
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="393"/>
-      <c r="G25" s="388"/>
+      <c r="F25" s="392"/>
+      <c r="G25" s="387"/>
     </row>
     <row r="26" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A26" s="41"/>
@@ -13635,8 +13639,8 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="393"/>
-      <c r="G26" s="388"/>
+      <c r="F26" s="392"/>
+      <c r="G26" s="387"/>
     </row>
     <row r="27" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A27" s="41"/>
@@ -13644,8 +13648,8 @@
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="393"/>
-      <c r="G27" s="388"/>
+      <c r="F27" s="392"/>
+      <c r="G27" s="387"/>
     </row>
     <row r="28" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A28" s="38"/>
@@ -13659,11 +13663,11 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="394" t="str">
+      <c r="F28" s="393" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="388"/>
+      <c r="G28" s="387"/>
     </row>
     <row r="29" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A29" s="38"/>
@@ -13677,11 +13681,11 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="394" t="str">
+      <c r="F29" s="393" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="388"/>
+      <c r="G29" s="387"/>
     </row>
     <row r="30" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A30" s="38"/>
@@ -13689,8 +13693,8 @@
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="395"/>
-      <c r="G30" s="396"/>
+      <c r="F30" s="394"/>
+      <c r="G30" s="395"/>
     </row>
     <row r="31" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A31" s="38"/>
@@ -13704,11 +13708,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="394" t="str">
+      <c r="F31" s="393" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="388"/>
+      <c r="G31" s="387"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -3476,7 +3476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="399">
+  <cellXfs count="398">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4670,9 +4670,6 @@
     </xf>
     <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="0" borderId="7" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8995,7 +8992,7 @@
           </r>
         </is>
       </c>
-      <c r="I23" s="398" t="str">
+      <c r="I23" s="11" t="str">
         <f>구매리스트!I9</f>
         <v>0</v>
       </c>
@@ -11385,7 +11382,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
-        <f>구매리스트!D11</f>
+        <f>TODAY()</f>
         <v>0</v>
       </c>
     </row>
@@ -12403,7 +12400,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="53" t="str">
-        <f>구매리스트!D11</f>
+        <f>TODAY()</f>
         <v>0</v>
       </c>
     </row>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="2" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="6" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -1940,7 +1940,7 @@
     <numFmt numFmtId="178" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="69">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -2569,33 +2569,6 @@
       <sz val="20"/>
       <color rgb="FF000000"/>
       <name val="Arial Narrow"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
-    </font>
-    <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
     </font>
     <font>
       <b val="0"/>
@@ -4614,15 +4587,6 @@
     <xf xfId="0" fontId="20" numFmtId="168" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="68" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="69" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="70" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="20" numFmtId="167" fillId="11" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4632,7 +4596,7 @@
     <xf xfId="0" fontId="18" numFmtId="179" fillId="0" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="71" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="68" numFmtId="0" fillId="4" borderId="13" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="63" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
@@ -4670,6 +4634,15 @@
     </xf>
     <xf xfId="0" fontId="11" numFmtId="0" fillId="0" borderId="56" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="20" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="24" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="19" numFmtId="49" fillId="0" borderId="61" applyFont="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10337,7 +10310,7 @@
         </is>
       </c>
       <c r="D21" s="304"/>
-      <c r="E21" s="396" t="s">
+      <c r="E21" s="393" t="s">
         <v>257</v>
       </c>
       <c r="F21" s="251"/>
@@ -11664,7 +11637,7 @@
         <f>구매리스트!D5</f>
         <v>0</v>
       </c>
-      <c r="E22" s="397">
+      <c r="E22" s="394">
         <v>1</v>
       </c>
       <c r="F22" s="256"/>
@@ -13330,7 +13303,7 @@
           </r>
         </is>
       </c>
-      <c r="F6" s="379"/>
+      <c r="F6" s="395"/>
       <c r="G6" s="377"/>
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
@@ -13342,7 +13315,7 @@
           </r>
         </is>
       </c>
-      <c r="F7" s="380"/>
+      <c r="F7" s="396"/>
       <c r="G7" s="377"/>
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
@@ -13354,7 +13327,7 @@
           </r>
         </is>
       </c>
-      <c r="F8" s="381"/>
+      <c r="F8" s="397"/>
       <c r="G8" s="377"/>
     </row>
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
@@ -13367,7 +13340,7 @@
           </r>
         </is>
       </c>
-      <c r="F9" s="379"/>
+      <c r="F9" s="395"/>
       <c r="G9" s="377"/>
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="246" customFormat="1">
@@ -13386,7 +13359,7 @@
           </r>
         </is>
       </c>
-      <c r="F11" s="382" t="str">
+      <c r="F11" s="379" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
@@ -13401,7 +13374,7 @@
           </r>
         </is>
       </c>
-      <c r="F12" s="382" t="str">
+      <c r="F12" s="379" t="str">
         <f>F31</f>
         <v>0</v>
       </c>
@@ -13418,7 +13391,7 @@
           </r>
         </is>
       </c>
-      <c r="F13" s="383" t="str">
+      <c r="F13" s="380" t="str">
         <f>SUM(F11-F12)</f>
         <v>0</v>
       </c>
@@ -13428,22 +13401,22 @@
       <c r="A14" s="245"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
-      <c r="E14" s="384"/>
+      <c r="E14" s="381"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
-      <c r="A15" s="385" t="inlineStr">
+      <c r="A15" s="382" t="inlineStr">
         <is>
           <r>
             <t xml:space="preserve">BANK ACCOUNT INFORMATION</t>
           </r>
         </is>
       </c>
-      <c r="B15" s="386"/>
-      <c r="C15" s="386"/>
-      <c r="D15" s="386"/>
-      <c r="E15" s="386"/>
-      <c r="F15" s="386"/>
-      <c r="G15" s="387"/>
+      <c r="B15" s="383"/>
+      <c r="C15" s="383"/>
+      <c r="D15" s="383"/>
+      <c r="E15" s="383"/>
+      <c r="F15" s="383"/>
+      <c r="G15" s="384"/>
     </row>
     <row r="16" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A16" s="240" t="inlineStr">
@@ -13453,11 +13426,11 @@
           </r>
         </is>
       </c>
-      <c r="B16" s="387"/>
-      <c r="C16" s="388" t="s">
+      <c r="B16" s="384"/>
+      <c r="C16" s="385" t="s">
         <v>360</v>
       </c>
-      <c r="D16" s="387"/>
+      <c r="D16" s="384"/>
       <c r="E16" s="240" t="inlineStr">
         <is>
           <r>
@@ -13465,10 +13438,10 @@
           </r>
         </is>
       </c>
-      <c r="F16" s="389" t="s">
+      <c r="F16" s="386" t="s">
         <v>362</v>
       </c>
-      <c r="G16" s="387"/>
+      <c r="G16" s="384"/>
     </row>
     <row r="17" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A17" s="240" t="inlineStr">
@@ -13478,11 +13451,11 @@
           </r>
         </is>
       </c>
-      <c r="B17" s="387"/>
-      <c r="C17" s="388" t="s">
+      <c r="B17" s="384"/>
+      <c r="C17" s="385" t="s">
         <v>364</v>
       </c>
-      <c r="D17" s="387"/>
+      <c r="D17" s="384"/>
       <c r="E17" s="240" t="inlineStr">
         <is>
           <r>
@@ -13493,7 +13466,7 @@
       <c r="F17" s="241" t="s">
         <v>366</v>
       </c>
-      <c r="G17" s="387"/>
+      <c r="G17" s="384"/>
     </row>
     <row r="18" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A18" s="240" t="inlineStr">
@@ -13503,11 +13476,11 @@
           </r>
         </is>
       </c>
-      <c r="B18" s="387"/>
-      <c r="C18" s="388" t="s">
+      <c r="B18" s="384"/>
+      <c r="C18" s="385" t="s">
         <v>368</v>
       </c>
-      <c r="D18" s="387"/>
+      <c r="D18" s="384"/>
       <c r="E18" s="240" t="inlineStr">
         <is>
           <r>
@@ -13515,15 +13488,15 @@
           </r>
         </is>
       </c>
-      <c r="F18" s="390" t="s">
+      <c r="F18" s="387" t="s">
         <v>370</v>
       </c>
-      <c r="G18" s="387"/>
+      <c r="G18" s="384"/>
     </row>
     <row r="19" spans="1:7">
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="384"/>
+      <c r="E19" s="381"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A20" s="42" t="inlineStr">
@@ -13568,7 +13541,7 @@
           </r>
         </is>
       </c>
-      <c r="G20" s="387"/>
+      <c r="G20" s="384"/>
     </row>
     <row r="21" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A21" s="133" t="str">
@@ -13588,11 +13561,11 @@
         <v>0</v>
       </c>
       <c r="E21" s="41"/>
-      <c r="F21" s="391" t="str">
+      <c r="F21" s="388" t="str">
         <f>차량인보이스!H22</f>
         <v>0</v>
       </c>
-      <c r="G21" s="387"/>
+      <c r="G21" s="384"/>
     </row>
     <row r="22" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A22" s="41"/>
@@ -13600,8 +13573,8 @@
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
       <c r="E22" s="41"/>
-      <c r="F22" s="392"/>
-      <c r="G22" s="387"/>
+      <c r="F22" s="389"/>
+      <c r="G22" s="384"/>
     </row>
     <row r="23" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A23" s="41"/>
@@ -13609,8 +13582,8 @@
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
-      <c r="F23" s="392"/>
-      <c r="G23" s="387"/>
+      <c r="F23" s="389"/>
+      <c r="G23" s="384"/>
     </row>
     <row r="24" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A24" s="41"/>
@@ -13618,8 +13591,8 @@
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
       <c r="E24" s="41"/>
-      <c r="F24" s="392"/>
-      <c r="G24" s="387"/>
+      <c r="F24" s="389"/>
+      <c r="G24" s="384"/>
     </row>
     <row r="25" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A25" s="41"/>
@@ -13627,8 +13600,8 @@
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
-      <c r="F25" s="392"/>
-      <c r="G25" s="387"/>
+      <c r="F25" s="389"/>
+      <c r="G25" s="384"/>
     </row>
     <row r="26" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A26" s="41"/>
@@ -13636,8 +13609,8 @@
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
-      <c r="F26" s="392"/>
-      <c r="G26" s="387"/>
+      <c r="F26" s="389"/>
+      <c r="G26" s="384"/>
     </row>
     <row r="27" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A27" s="41"/>
@@ -13645,8 +13618,8 @@
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
       <c r="E27" s="41"/>
-      <c r="F27" s="392"/>
-      <c r="G27" s="387"/>
+      <c r="F27" s="389"/>
+      <c r="G27" s="384"/>
     </row>
     <row r="28" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A28" s="38"/>
@@ -13660,11 +13633,11 @@
           </r>
         </is>
       </c>
-      <c r="F28" s="393" t="str">
+      <c r="F28" s="390" t="str">
         <f>SUM(F21:G27)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="387"/>
+      <c r="G28" s="384"/>
     </row>
     <row r="29" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A29" s="38"/>
@@ -13678,11 +13651,11 @@
           </r>
         </is>
       </c>
-      <c r="F29" s="393" t="str">
+      <c r="F29" s="390" t="str">
         <f>차량인보이스!I22</f>
         <v>0</v>
       </c>
-      <c r="G29" s="387"/>
+      <c r="G29" s="384"/>
     </row>
     <row r="30" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A30" s="38"/>
@@ -13690,8 +13663,8 @@
       <c r="C30" s="40"/>
       <c r="D30" s="40"/>
       <c r="E30" s="50"/>
-      <c r="F30" s="394"/>
-      <c r="G30" s="395"/>
+      <c r="F30" s="391"/>
+      <c r="G30" s="392"/>
     </row>
     <row r="31" spans="1:7" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A31" s="38"/>
@@ -13705,11 +13678,11 @@
           </r>
         </is>
       </c>
-      <c r="F31" s="393" t="str">
+      <c r="F31" s="390" t="str">
         <f>SUM(F28:G29)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="387"/>
+      <c r="G31" s="384"/>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="38"/>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -4692,22 +4692,17 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>600075</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1057275" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 32" descr=""/>
+        <xdr:cNvPr id="2" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -4719,16 +4714,14 @@
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1057275" cy="1028700"/>
-        </a:xfrm>
+        <a:xfrm rot="0"/>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4773,43 +4766,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>457200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 4" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1057275" cy="1028700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -4823,13 +4779,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 12" descr=""/>
+        <xdr:cNvPr id="2" name="그림 12" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4845,6 +4801,36 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>638175</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4889,43 +4875,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 4" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0">
-          <a:ext cx="1247775" cy="1228725"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>48</xdr:row>
@@ -4939,13 +4888,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 7" descr=""/>
+        <xdr:cNvPr id="2" name="그림 7" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4961,6 +4910,36 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1247775" cy="1228725"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -1778,7 +1778,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">PROFORM INVOICE</t>
+      <t xml:space="preserve">PROFORMA INVOICE</t>
     </r>
   </si>
   <si>
@@ -1801,7 +1801,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Adress</t>
+      <t xml:space="preserve">Address</t>
     </r>
   </si>
   <si>
@@ -1852,7 +1852,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Swift Cose</t>
+      <t xml:space="preserve">Swift Code</t>
     </r>
   </si>
   <si>
@@ -1860,7 +1860,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Bank Adress</t>
+      <t xml:space="preserve">Bank Address</t>
     </r>
   </si>
   <si>
@@ -1876,7 +1876,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beneficiary Adress</t>
+      <t xml:space="preserve">Beneficiary Address</t>
     </r>
   </si>
   <si>
@@ -4655,6 +4655,36 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm rot="0"/>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4670,13 +4700,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 30" descr=""/>
+        <xdr:cNvPr id="2" name="그림 30" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4692,23 +4722,28 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
+      <xdr:colOff>638175</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1057275" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="govt_seal" descr=""/>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4722,11 +4757,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4742,13 +4772,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 3" descr=""/>
+        <xdr:cNvPr id="2" name="그림 3" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4779,13 +4809,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 12" descr=""/>
+        <xdr:cNvPr id="3" name="그림 12" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4801,23 +4831,28 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>638175</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>447675</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1057275" cy="1028700"/>
+    <xdr:ext cx="1247775" cy="1228725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
+        <xdr:cNvPr id="1" name="govt_seal" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4831,11 +4866,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -4851,13 +4881,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="그림 2" descr=""/>
+        <xdr:cNvPr id="2" name="그림 2" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4888,13 +4918,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="그림 7" descr=""/>
+        <xdr:cNvPr id="3" name="그림 7" descr=""/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -4910,36 +4940,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>447675</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1247775" cy="1228725"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="govt_seal" descr=""/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm rot="0"/>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5512,7 +5512,20 @@
     <col min="12" max="12" width="11.75" customWidth="true" style="246"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="246" customFormat="1"/>
+    <row r="1" spans="1:12" customHeight="1" ht="26.25" s="246" customFormat="1">
+      <c r="A1" s="246"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+    </row>
     <row r="2" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A2" s="105" t="inlineStr">
         <is>
@@ -5521,6 +5534,10 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
       <c r="F2" s="105" t="inlineStr">
         <is>
           <r>
@@ -5528,6 +5545,12 @@
           </r>
         </is>
       </c>
+      <c r="G2" s="246"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
     </row>
     <row r="3" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A3" s="103" t="inlineStr">
@@ -5552,6 +5575,7 @@
         </is>
       </c>
       <c r="D3" s="113"/>
+      <c r="E3" s="246"/>
       <c r="F3" s="106" t="inlineStr">
         <is>
           <r>
@@ -5570,6 +5594,9 @@
       <c r="I3" s="115">
         <v>45875</v>
       </c>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
     </row>
     <row r="4" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A4" s="103" t="inlineStr">
@@ -5629,6 +5656,9 @@
           </r>
         </is>
       </c>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
     </row>
     <row r="5" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A5" s="103" t="inlineStr">
@@ -5688,6 +5718,9 @@
           </r>
         </is>
       </c>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
     </row>
     <row r="6" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A6" s="103" t="inlineStr">
@@ -5736,6 +5769,9 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
         <v>0</v>
       </c>
+      <c r="J6" s="246"/>
+      <c r="K6" s="246"/>
+      <c r="L6" s="246"/>
     </row>
     <row r="7" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A7" s="103" t="inlineStr">
@@ -5779,6 +5815,9 @@
       <c r="I7" s="113">
         <v>1860</v>
       </c>
+      <c r="J7" s="246"/>
+      <c r="K7" s="246"/>
+      <c r="L7" s="246"/>
     </row>
     <row r="8" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A8" s="103" t="inlineStr">
@@ -5822,6 +5861,9 @@
       <c r="I8" s="113">
         <v>2095</v>
       </c>
+      <c r="J8" s="246"/>
+      <c r="K8" s="246"/>
+      <c r="L8" s="246"/>
     </row>
     <row r="9" spans="1:12" customHeight="1" ht="22.5" s="246" customFormat="1">
       <c r="A9" s="105" t="inlineStr">
@@ -5859,6 +5901,9 @@
           </r>
         </is>
       </c>
+      <c r="J9" s="246"/>
+      <c r="K9" s="246"/>
+      <c r="L9" s="246"/>
     </row>
     <row r="10" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A10" s="103" t="inlineStr">
@@ -5914,6 +5959,9 @@
       <c r="I10" s="115">
         <v>45775</v>
       </c>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
     </row>
     <row r="11" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A11" s="103" t="inlineStr">
@@ -5969,6 +6017,9 @@
       <c r="I11" s="115">
         <v>46504</v>
       </c>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
     </row>
     <row r="12" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A12" s="103" t="inlineStr">
@@ -6024,6 +6075,9 @@
       <c r="I12" s="113">
         <v>163268</v>
       </c>
+      <c r="J12" s="246"/>
+      <c r="K12" s="246"/>
+      <c r="L12" s="246"/>
     </row>
     <row r="13" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A13" s="105" t="inlineStr">
@@ -6056,6 +6110,9 @@
         <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
         <v>0</v>
       </c>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
+      <c r="L13" s="246"/>
     </row>
     <row r="14" spans="1:12" customHeight="1" ht="120.75" s="246" customFormat="1">
       <c r="A14" s="103" t="inlineStr">
@@ -6091,6 +6148,11 @@
       <c r="E14" s="100"/>
       <c r="F14" s="100"/>
       <c r="G14" s="100"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
     </row>
     <row r="15" spans="1:12" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A15" s="103" t="inlineStr">
@@ -6122,11 +6184,15 @@
           </r>
         </is>
       </c>
+      <c r="H15" s="246"/>
       <c r="I15" s="246" t="str">
         <f t="array" ref="I15" aca="1" ca="1">_xlfn.TEXTJOIN(",",,
  _xlfn.UNIQUE(_xlfn.IFNA(INDEX({"GASOLIN","DIESEL","LPG"},
  MATCH(G15,{"휘발유","경유","LPG"},0)),""),1))</f>
       </c>
+      <c r="J15" s="246"/>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246"/>
     </row>
     <row r="16" spans="1:12" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A16" s="100"/>
@@ -6145,6 +6211,7 @@
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
       <c r="G16" s="100"/>
+      <c r="H16" s="246"/>
       <c r="I16" s="246" t="inlineStr">
         <is>
           <r>
@@ -6152,6 +6219,9 @@
           </r>
         </is>
       </c>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="100"/>
@@ -6161,6 +6231,11 @@
       <c r="E17" s="100"/>
       <c r="F17" s="100"/>
       <c r="G17" s="100"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
+      <c r="L17" s="246"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="100"/>
@@ -6176,6 +6251,11 @@
           </r>
         </is>
       </c>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
+      <c r="L18" s="246"/>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" s="100"/>
@@ -6185,6 +6265,11 @@
       <c r="E19" s="100"/>
       <c r="F19" s="100"/>
       <c r="G19" s="100"/>
+      <c r="H19" s="246"/>
+      <c r="I19" s="246"/>
+      <c r="J19" s="246"/>
+      <c r="K19" s="246"/>
+      <c r="L19" s="246"/>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" s="100"/>
@@ -6194,6 +6279,11 @@
       <c r="E20" s="100"/>
       <c r="F20" s="100"/>
       <c r="G20" s="100"/>
+      <c r="H20" s="246"/>
+      <c r="I20" s="246"/>
+      <c r="J20" s="246"/>
+      <c r="K20" s="246"/>
+      <c r="L20" s="246"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="100"/>
@@ -6203,8 +6293,28 @@
       <c r="E21" s="100"/>
       <c r="F21" s="100"/>
       <c r="G21" s="100"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
+      <c r="L21" s="246"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="246"/>
+      <c r="B22" s="246"/>
+      <c r="C22" s="246"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="246"/>
+      <c r="F22" s="246"/>
+      <c r="G22" s="246"/>
+      <c r="H22" s="246"/>
+      <c r="I22" s="246"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="246"/>
+      <c r="L22" s="246"/>
     </row>
     <row r="23" spans="1:12">
+      <c r="A23" s="246"/>
       <c r="B23" s="108" t="inlineStr">
         <is>
           <r>
@@ -6212,6 +6322,7 @@
           </r>
         </is>
       </c>
+      <c r="C23" s="246"/>
       <c r="D23" s="108" t="inlineStr">
         <is>
           <r>
@@ -6219,8 +6330,17 @@
           </r>
         </is>
       </c>
+      <c r="E23" s="246"/>
+      <c r="F23" s="246"/>
+      <c r="G23" s="246"/>
+      <c r="H23" s="246"/>
+      <c r="I23" s="246"/>
+      <c r="J23" s="246"/>
+      <c r="K23" s="246"/>
+      <c r="L23" s="246"/>
     </row>
     <row r="24" spans="1:12">
+      <c r="A24" s="246"/>
       <c r="B24" s="108" t="inlineStr">
         <is>
           <r>
@@ -6228,6 +6348,7 @@
           </r>
         </is>
       </c>
+      <c r="C24" s="246"/>
       <c r="D24" s="108" t="inlineStr">
         <is>
           <r>
@@ -6235,9 +6356,17 @@
           </r>
         </is>
       </c>
+      <c r="E24" s="246"/>
       <c r="F24" s="108"/>
+      <c r="G24" s="246"/>
+      <c r="H24" s="246"/>
+      <c r="I24" s="246"/>
+      <c r="J24" s="246"/>
+      <c r="K24" s="246"/>
+      <c r="L24" s="246"/>
     </row>
     <row r="25" spans="1:12">
+      <c r="A25" s="246"/>
       <c r="B25" s="108" t="inlineStr">
         <is>
           <r>
@@ -6245,6 +6374,7 @@
           </r>
         </is>
       </c>
+      <c r="C25" s="246"/>
       <c r="D25" s="108" t="inlineStr">
         <is>
           <r>
@@ -6252,9 +6382,17 @@
           </r>
         </is>
       </c>
+      <c r="E25" s="246"/>
       <c r="F25" s="108"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
+      <c r="L25" s="246"/>
     </row>
     <row r="26" spans="1:12">
+      <c r="A26" s="246"/>
       <c r="B26" s="108" t="inlineStr">
         <is>
           <r>
@@ -6262,6 +6400,7 @@
           </r>
         </is>
       </c>
+      <c r="C26" s="246"/>
       <c r="D26" s="108" t="inlineStr">
         <is>
           <r>
@@ -6269,9 +6408,19 @@
           </r>
         </is>
       </c>
+      <c r="E26" s="246"/>
       <c r="F26" s="108"/>
+      <c r="G26" s="246"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
+      <c r="L26" s="246"/>
     </row>
     <row r="27" spans="1:12">
+      <c r="A27" s="246"/>
+      <c r="B27" s="246"/>
+      <c r="C27" s="246"/>
       <c r="D27" s="108" t="inlineStr">
         <is>
           <r>
@@ -6279,9 +6428,19 @@
           </r>
         </is>
       </c>
+      <c r="E27" s="246"/>
       <c r="F27" s="108"/>
+      <c r="G27" s="246"/>
+      <c r="H27" s="246"/>
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
+      <c r="L27" s="246"/>
     </row>
     <row r="28" spans="1:12">
+      <c r="A28" s="246"/>
+      <c r="B28" s="246"/>
+      <c r="C28" s="246"/>
       <c r="D28" s="108" t="inlineStr">
         <is>
           <r>
@@ -6289,9 +6448,19 @@
           </r>
         </is>
       </c>
+      <c r="E28" s="246"/>
       <c r="F28" s="108"/>
+      <c r="G28" s="246"/>
+      <c r="H28" s="246"/>
+      <c r="I28" s="246"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="246"/>
+      <c r="L28" s="246"/>
     </row>
     <row r="29" spans="1:12">
+      <c r="A29" s="246"/>
+      <c r="B29" s="246"/>
+      <c r="C29" s="246"/>
       <c r="D29" s="109" t="inlineStr">
         <is>
           <r>
@@ -6299,9 +6468,19 @@
           </r>
         </is>
       </c>
+      <c r="E29" s="246"/>
       <c r="F29" s="108"/>
+      <c r="G29" s="246"/>
+      <c r="H29" s="246"/>
+      <c r="I29" s="246"/>
+      <c r="J29" s="246"/>
+      <c r="K29" s="246"/>
+      <c r="L29" s="246"/>
     </row>
     <row r="30" spans="1:12">
+      <c r="A30" s="246"/>
+      <c r="B30" s="246"/>
+      <c r="C30" s="246"/>
       <c r="D30" s="108" t="inlineStr">
         <is>
           <r>
@@ -6309,8 +6488,19 @@
           </r>
         </is>
       </c>
+      <c r="E30" s="246"/>
+      <c r="F30" s="246"/>
+      <c r="G30" s="246"/>
+      <c r="H30" s="246"/>
+      <c r="I30" s="246"/>
+      <c r="J30" s="246"/>
+      <c r="K30" s="246"/>
+      <c r="L30" s="246"/>
     </row>
     <row r="31" spans="1:12">
+      <c r="A31" s="246"/>
+      <c r="B31" s="246"/>
+      <c r="C31" s="246"/>
       <c r="D31" s="108" t="inlineStr">
         <is>
           <r>
@@ -6318,8 +6508,19 @@
           </r>
         </is>
       </c>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
+      <c r="G31" s="246"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
     </row>
     <row r="32" spans="1:12">
+      <c r="A32" s="246"/>
+      <c r="B32" s="246"/>
+      <c r="C32" s="246"/>
       <c r="D32" s="108" t="inlineStr">
         <is>
           <r>
@@ -6327,8 +6528,19 @@
           </r>
         </is>
       </c>
+      <c r="E32" s="246"/>
+      <c r="F32" s="246"/>
+      <c r="G32" s="246"/>
+      <c r="H32" s="246"/>
+      <c r="I32" s="246"/>
+      <c r="J32" s="246"/>
+      <c r="K32" s="246"/>
+      <c r="L32" s="246"/>
     </row>
     <row r="33" spans="1:12">
+      <c r="A33" s="246"/>
+      <c r="B33" s="246"/>
+      <c r="C33" s="246"/>
       <c r="D33" s="108" t="inlineStr">
         <is>
           <r>
@@ -6336,8 +6548,19 @@
           </r>
         </is>
       </c>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
+      <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
+      <c r="L33" s="246"/>
     </row>
     <row r="34" spans="1:12">
+      <c r="A34" s="246"/>
+      <c r="B34" s="246"/>
+      <c r="C34" s="246"/>
       <c r="D34" s="108" t="inlineStr">
         <is>
           <r>
@@ -6345,8 +6568,19 @@
           </r>
         </is>
       </c>
+      <c r="E34" s="246"/>
+      <c r="F34" s="246"/>
+      <c r="G34" s="246"/>
+      <c r="H34" s="246"/>
+      <c r="I34" s="246"/>
+      <c r="J34" s="246"/>
+      <c r="K34" s="246"/>
+      <c r="L34" s="246"/>
     </row>
     <row r="35" spans="1:12">
+      <c r="A35" s="246"/>
+      <c r="B35" s="246"/>
+      <c r="C35" s="246"/>
       <c r="D35" s="108" t="inlineStr">
         <is>
           <r>
@@ -6354,8 +6588,19 @@
           </r>
         </is>
       </c>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
+      <c r="G35" s="246"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246"/>
     </row>
     <row r="36" spans="1:12">
+      <c r="A36" s="246"/>
+      <c r="B36" s="246"/>
+      <c r="C36" s="246"/>
       <c r="D36" s="108" t="inlineStr">
         <is>
           <r>
@@ -6363,8 +6608,19 @@
           </r>
         </is>
       </c>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
+      <c r="G36" s="246"/>
+      <c r="H36" s="246"/>
+      <c r="I36" s="246"/>
+      <c r="J36" s="246"/>
+      <c r="K36" s="246"/>
+      <c r="L36" s="246"/>
     </row>
     <row r="37" spans="1:12">
+      <c r="A37" s="246"/>
+      <c r="B37" s="246"/>
+      <c r="C37" s="246"/>
       <c r="D37" s="108" t="inlineStr">
         <is>
           <r>
@@ -6372,8 +6628,19 @@
           </r>
         </is>
       </c>
+      <c r="E37" s="246"/>
+      <c r="F37" s="246"/>
+      <c r="G37" s="246"/>
+      <c r="H37" s="246"/>
+      <c r="I37" s="246"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246"/>
+      <c r="L37" s="246"/>
     </row>
     <row r="38" spans="1:12">
+      <c r="A38" s="246"/>
+      <c r="B38" s="246"/>
+      <c r="C38" s="246"/>
       <c r="D38" s="108" t="inlineStr">
         <is>
           <r>
@@ -6381,8 +6648,19 @@
           </r>
         </is>
       </c>
+      <c r="E38" s="246"/>
+      <c r="F38" s="246"/>
+      <c r="G38" s="246"/>
+      <c r="H38" s="246"/>
+      <c r="I38" s="246"/>
+      <c r="J38" s="246"/>
+      <c r="K38" s="246"/>
+      <c r="L38" s="246"/>
     </row>
     <row r="39" spans="1:12">
+      <c r="A39" s="246"/>
+      <c r="B39" s="246"/>
+      <c r="C39" s="246"/>
       <c r="D39" s="108" t="inlineStr">
         <is>
           <r>
@@ -6390,86 +6668,380 @@
           </r>
         </is>
       </c>
+      <c r="E39" s="246"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+      <c r="I39" s="246"/>
+      <c r="J39" s="246"/>
+      <c r="K39" s="246"/>
+      <c r="L39" s="246"/>
     </row>
     <row r="40" spans="1:12">
+      <c r="A40" s="246"/>
+      <c r="B40" s="246"/>
+      <c r="C40" s="246"/>
       <c r="D40" s="108">
         <v>123456</v>
       </c>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
     </row>
     <row r="41" spans="1:12">
+      <c r="A41" s="246"/>
+      <c r="B41" s="246"/>
+      <c r="C41" s="246"/>
       <c r="D41" s="108"/>
+      <c r="E41" s="246"/>
+      <c r="F41" s="246"/>
+      <c r="G41" s="246"/>
+      <c r="H41" s="246"/>
+      <c r="I41" s="246"/>
+      <c r="J41" s="246"/>
+      <c r="K41" s="246"/>
+      <c r="L41" s="246"/>
     </row>
     <row r="42" spans="1:12">
+      <c r="A42" s="246"/>
+      <c r="B42" s="246"/>
+      <c r="C42" s="246"/>
       <c r="D42" s="108"/>
+      <c r="E42" s="246"/>
+      <c r="F42" s="246"/>
+      <c r="G42" s="246"/>
+      <c r="H42" s="246"/>
+      <c r="I42" s="246"/>
+      <c r="J42" s="246"/>
+      <c r="K42" s="246"/>
+      <c r="L42" s="246"/>
     </row>
     <row r="43" spans="1:12">
+      <c r="A43" s="246"/>
+      <c r="B43" s="246"/>
+      <c r="C43" s="246"/>
       <c r="D43" s="108"/>
+      <c r="E43" s="246"/>
+      <c r="F43" s="246"/>
+      <c r="G43" s="246"/>
+      <c r="H43" s="246"/>
+      <c r="I43" s="246"/>
+      <c r="J43" s="246"/>
+      <c r="K43" s="246"/>
+      <c r="L43" s="246"/>
     </row>
     <row r="44" spans="1:12">
+      <c r="A44" s="246"/>
+      <c r="B44" s="246"/>
+      <c r="C44" s="246"/>
       <c r="D44" s="108"/>
+      <c r="E44" s="246"/>
+      <c r="F44" s="246"/>
+      <c r="G44" s="246"/>
+      <c r="H44" s="246"/>
+      <c r="I44" s="246"/>
+      <c r="J44" s="246"/>
+      <c r="K44" s="246"/>
+      <c r="L44" s="246"/>
     </row>
     <row r="45" spans="1:12">
+      <c r="A45" s="246"/>
+      <c r="B45" s="246"/>
+      <c r="C45" s="246"/>
       <c r="D45" s="108"/>
+      <c r="E45" s="246"/>
+      <c r="F45" s="246"/>
+      <c r="G45" s="246"/>
+      <c r="H45" s="246"/>
+      <c r="I45" s="246"/>
+      <c r="J45" s="246"/>
+      <c r="K45" s="246"/>
+      <c r="L45" s="246"/>
     </row>
     <row r="46" spans="1:12">
+      <c r="A46" s="246"/>
+      <c r="B46" s="246"/>
+      <c r="C46" s="246"/>
       <c r="D46" s="108"/>
+      <c r="E46" s="246"/>
+      <c r="F46" s="246"/>
+      <c r="G46" s="246"/>
+      <c r="H46" s="246"/>
+      <c r="I46" s="246"/>
+      <c r="J46" s="246"/>
+      <c r="K46" s="246"/>
+      <c r="L46" s="246"/>
     </row>
     <row r="47" spans="1:12">
+      <c r="A47" s="246"/>
+      <c r="B47" s="246"/>
+      <c r="C47" s="246"/>
       <c r="D47" s="108"/>
+      <c r="E47" s="246"/>
+      <c r="F47" s="246"/>
+      <c r="G47" s="246"/>
+      <c r="H47" s="246"/>
+      <c r="I47" s="246"/>
+      <c r="J47" s="246"/>
+      <c r="K47" s="246"/>
+      <c r="L47" s="246"/>
     </row>
     <row r="48" spans="1:12">
+      <c r="A48" s="246"/>
+      <c r="B48" s="246"/>
+      <c r="C48" s="246"/>
       <c r="D48" s="108"/>
+      <c r="E48" s="246"/>
+      <c r="F48" s="246"/>
+      <c r="G48" s="246"/>
+      <c r="H48" s="246"/>
+      <c r="I48" s="246"/>
+      <c r="J48" s="246"/>
+      <c r="K48" s="246"/>
+      <c r="L48" s="246"/>
     </row>
     <row r="49" spans="1:12">
+      <c r="A49" s="246"/>
+      <c r="B49" s="246"/>
+      <c r="C49" s="246"/>
       <c r="D49" s="108"/>
+      <c r="E49" s="246"/>
+      <c r="F49" s="246"/>
+      <c r="G49" s="246"/>
+      <c r="H49" s="246"/>
+      <c r="I49" s="246"/>
+      <c r="J49" s="246"/>
+      <c r="K49" s="246"/>
+      <c r="L49" s="246"/>
     </row>
     <row r="50" spans="1:12">
+      <c r="A50" s="246"/>
+      <c r="B50" s="246"/>
+      <c r="C50" s="246"/>
       <c r="D50" s="108"/>
+      <c r="E50" s="246"/>
+      <c r="F50" s="246"/>
+      <c r="G50" s="246"/>
+      <c r="H50" s="246"/>
+      <c r="I50" s="246"/>
+      <c r="J50" s="246"/>
+      <c r="K50" s="246"/>
+      <c r="L50" s="246"/>
     </row>
     <row r="51" spans="1:12">
+      <c r="A51" s="246"/>
+      <c r="B51" s="246"/>
+      <c r="C51" s="246"/>
       <c r="D51" s="108"/>
+      <c r="E51" s="246"/>
+      <c r="F51" s="246"/>
+      <c r="G51" s="246"/>
+      <c r="H51" s="246"/>
+      <c r="I51" s="246"/>
+      <c r="J51" s="246"/>
+      <c r="K51" s="246"/>
+      <c r="L51" s="246"/>
     </row>
     <row r="52" spans="1:12">
+      <c r="A52" s="246"/>
+      <c r="B52" s="246"/>
+      <c r="C52" s="246"/>
       <c r="D52" s="108"/>
+      <c r="E52" s="246"/>
+      <c r="F52" s="246"/>
+      <c r="G52" s="246"/>
+      <c r="H52" s="246"/>
+      <c r="I52" s="246"/>
+      <c r="J52" s="246"/>
+      <c r="K52" s="246"/>
+      <c r="L52" s="246"/>
     </row>
     <row r="53" spans="1:12">
+      <c r="A53" s="246"/>
+      <c r="B53" s="246"/>
+      <c r="C53" s="246"/>
       <c r="D53" s="108"/>
+      <c r="E53" s="246"/>
+      <c r="F53" s="246"/>
+      <c r="G53" s="246"/>
+      <c r="H53" s="246"/>
+      <c r="I53" s="246"/>
+      <c r="J53" s="246"/>
+      <c r="K53" s="246"/>
+      <c r="L53" s="246"/>
     </row>
     <row r="54" spans="1:12">
+      <c r="A54" s="246"/>
+      <c r="B54" s="246"/>
+      <c r="C54" s="246"/>
       <c r="D54" s="108"/>
+      <c r="E54" s="246"/>
+      <c r="F54" s="246"/>
+      <c r="G54" s="246"/>
+      <c r="H54" s="246"/>
+      <c r="I54" s="246"/>
+      <c r="J54" s="246"/>
+      <c r="K54" s="246"/>
+      <c r="L54" s="246"/>
     </row>
     <row r="55" spans="1:12">
+      <c r="A55" s="246"/>
+      <c r="B55" s="246"/>
+      <c r="C55" s="246"/>
       <c r="D55" s="108"/>
+      <c r="E55" s="246"/>
+      <c r="F55" s="246"/>
+      <c r="G55" s="246"/>
+      <c r="H55" s="246"/>
+      <c r="I55" s="246"/>
+      <c r="J55" s="246"/>
+      <c r="K55" s="246"/>
+      <c r="L55" s="246"/>
     </row>
     <row r="56" spans="1:12">
+      <c r="A56" s="246"/>
+      <c r="B56" s="246"/>
+      <c r="C56" s="246"/>
       <c r="D56" s="108"/>
+      <c r="E56" s="246"/>
+      <c r="F56" s="246"/>
+      <c r="G56" s="246"/>
+      <c r="H56" s="246"/>
+      <c r="I56" s="246"/>
+      <c r="J56" s="246"/>
+      <c r="K56" s="246"/>
+      <c r="L56" s="246"/>
     </row>
     <row r="57" spans="1:12">
+      <c r="A57" s="246"/>
+      <c r="B57" s="246"/>
+      <c r="C57" s="246"/>
       <c r="D57" s="108"/>
+      <c r="E57" s="246"/>
+      <c r="F57" s="246"/>
+      <c r="G57" s="246"/>
+      <c r="H57" s="246"/>
+      <c r="I57" s="246"/>
+      <c r="J57" s="246"/>
+      <c r="K57" s="246"/>
+      <c r="L57" s="246"/>
     </row>
     <row r="58" spans="1:12">
+      <c r="A58" s="246"/>
+      <c r="B58" s="246"/>
+      <c r="C58" s="246"/>
       <c r="D58" s="108"/>
+      <c r="E58" s="246"/>
+      <c r="F58" s="246"/>
+      <c r="G58" s="246"/>
+      <c r="H58" s="246"/>
+      <c r="I58" s="246"/>
+      <c r="J58" s="246"/>
+      <c r="K58" s="246"/>
+      <c r="L58" s="246"/>
     </row>
     <row r="59" spans="1:12">
+      <c r="A59" s="246"/>
+      <c r="B59" s="246"/>
+      <c r="C59" s="246"/>
       <c r="D59" s="108"/>
+      <c r="E59" s="246"/>
+      <c r="F59" s="246"/>
+      <c r="G59" s="246"/>
+      <c r="H59" s="246"/>
+      <c r="I59" s="246"/>
+      <c r="J59" s="246"/>
+      <c r="K59" s="246"/>
+      <c r="L59" s="246"/>
     </row>
     <row r="60" spans="1:12">
+      <c r="A60" s="246"/>
+      <c r="B60" s="246"/>
+      <c r="C60" s="246"/>
       <c r="D60" s="108"/>
+      <c r="E60" s="246"/>
+      <c r="F60" s="246"/>
+      <c r="G60" s="246"/>
+      <c r="H60" s="246"/>
+      <c r="I60" s="246"/>
+      <c r="J60" s="246"/>
+      <c r="K60" s="246"/>
+      <c r="L60" s="246"/>
     </row>
     <row r="61" spans="1:12">
+      <c r="A61" s="246"/>
+      <c r="B61" s="246"/>
+      <c r="C61" s="246"/>
       <c r="D61" s="108"/>
+      <c r="E61" s="246"/>
+      <c r="F61" s="246"/>
+      <c r="G61" s="246"/>
+      <c r="H61" s="246"/>
+      <c r="I61" s="246"/>
+      <c r="J61" s="246"/>
+      <c r="K61" s="246"/>
+      <c r="L61" s="246"/>
     </row>
     <row r="62" spans="1:12">
+      <c r="A62" s="246"/>
+      <c r="B62" s="246"/>
+      <c r="C62" s="246"/>
       <c r="D62" s="108"/>
+      <c r="E62" s="246"/>
+      <c r="F62" s="246"/>
+      <c r="G62" s="246"/>
+      <c r="H62" s="246"/>
+      <c r="I62" s="246"/>
+      <c r="J62" s="246"/>
+      <c r="K62" s="246"/>
+      <c r="L62" s="246"/>
     </row>
     <row r="63" spans="1:12">
+      <c r="A63" s="246"/>
+      <c r="B63" s="246"/>
+      <c r="C63" s="246"/>
       <c r="D63" s="108"/>
+      <c r="E63" s="246"/>
+      <c r="F63" s="246"/>
+      <c r="G63" s="246"/>
+      <c r="H63" s="246"/>
+      <c r="I63" s="246"/>
+      <c r="J63" s="246"/>
+      <c r="K63" s="246"/>
+      <c r="L63" s="246"/>
     </row>
     <row r="64" spans="1:12">
+      <c r="A64" s="246"/>
+      <c r="B64" s="246"/>
+      <c r="C64" s="246"/>
       <c r="D64" s="108"/>
+      <c r="E64" s="246"/>
+      <c r="F64" s="246"/>
+      <c r="G64" s="246"/>
+      <c r="H64" s="246"/>
+      <c r="I64" s="246"/>
+      <c r="J64" s="246"/>
+      <c r="K64" s="246"/>
+      <c r="L64" s="246"/>
     </row>
     <row r="65" spans="1:12">
+      <c r="A65" s="246"/>
+      <c r="B65" s="246"/>
+      <c r="C65" s="246"/>
       <c r="D65" s="108"/>
+      <c r="E65" s="246"/>
+      <c r="F65" s="246"/>
+      <c r="G65" s="246"/>
+      <c r="H65" s="246"/>
+      <c r="I65" s="246"/>
+      <c r="J65" s="246"/>
+      <c r="K65" s="246"/>
+      <c r="L65" s="246"/>
     </row>
   </sheetData>
   <dataValidations count="5">
@@ -6561,6 +7133,9 @@
           </r>
         </is>
       </c>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
     </row>
     <row r="2" spans="1:20" customHeight="1" ht="60" s="246" customFormat="1">
       <c r="A2" s="250" t="inlineStr">
@@ -6586,6 +7161,9 @@
       <c r="O2" s="251"/>
       <c r="P2" s="251"/>
       <c r="Q2" s="252"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
     </row>
     <row r="3" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A3" s="1"/>
@@ -6628,12 +7206,16 @@
           </r>
         </is>
       </c>
+      <c r="N3" s="246"/>
       <c r="O3" s="150" t="str">
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
       <c r="P3" s="253"/>
       <c r="Q3" s="254"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
     </row>
     <row r="4" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A4" s="135" t="inlineStr">
@@ -6683,6 +7265,9 @@
         </is>
       </c>
       <c r="Q4" s="256"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
     </row>
     <row r="5" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A5" s="136" t="inlineStr">
@@ -6723,6 +7308,9 @@
         <v>0</v>
       </c>
       <c r="Q5" s="256"/>
+      <c r="R5" s="246"/>
+      <c r="S5" s="246"/>
+      <c r="T5" s="246"/>
     </row>
     <row r="6" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A6" s="136" t="inlineStr">
@@ -6760,6 +7348,9 @@
       <c r="O6" s="255"/>
       <c r="P6" s="255"/>
       <c r="Q6" s="256"/>
+      <c r="R6" s="246"/>
+      <c r="S6" s="246"/>
+      <c r="T6" s="246"/>
     </row>
     <row r="7" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A7" s="136" t="inlineStr">
@@ -6787,6 +7378,9 @@
       <c r="O7" s="255"/>
       <c r="P7" s="255"/>
       <c r="Q7" s="256"/>
+      <c r="R7" s="246"/>
+      <c r="S7" s="246"/>
+      <c r="T7" s="246"/>
     </row>
     <row r="8" spans="1:20" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A8" s="259" t="inlineStr">
@@ -6833,6 +7427,8 @@
       <c r="O8" s="255"/>
       <c r="P8" s="255"/>
       <c r="Q8" s="256"/>
+      <c r="R8" s="246"/>
+      <c r="S8" s="246"/>
       <c r="T8" s="246" t="inlineStr">
         <is>
           <r>
@@ -6859,6 +7455,9 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
     </row>
     <row r="10" spans="1:20" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A10" s="262" t="inlineStr">
@@ -6868,7 +7467,25 @@
           </r>
         </is>
       </c>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="246"/>
+      <c r="O10" s="246"/>
+      <c r="P10" s="246"/>
       <c r="Q10" s="263"/>
+      <c r="R10" s="246"/>
+      <c r="S10" s="246"/>
+      <c r="T10" s="246"/>
     </row>
     <row r="11" spans="1:20" customHeight="1" ht="22.5" s="246" customFormat="1">
       <c r="A11" s="1"/>
@@ -6879,7 +7496,24 @@
           </r>
         </is>
       </c>
+      <c r="C11" s="246"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
+      <c r="M11" s="246"/>
+      <c r="N11" s="246"/>
+      <c r="O11" s="246"/>
+      <c r="P11" s="246"/>
       <c r="Q11" s="263"/>
+      <c r="R11" s="246"/>
+      <c r="S11" s="246"/>
+      <c r="T11" s="246"/>
     </row>
     <row r="12" spans="1:20" customHeight="1" ht="20.25" s="246" customFormat="1">
       <c r="A12" s="1"/>
@@ -6899,6 +7533,9 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="246"/>
+      <c r="S12" s="246"/>
+      <c r="T12" s="246"/>
     </row>
     <row r="13" spans="1:20" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
@@ -6915,24 +7552,60 @@
           </r>
         </is>
       </c>
+      <c r="C13" s="246"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
       <c r="L13" s="155" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
+      <c r="M13" s="246"/>
+      <c r="N13" s="246"/>
       <c r="O13" s="246"/>
       <c r="P13" s="264"/>
       <c r="Q13" s="5"/>
+      <c r="R13" s="246"/>
+      <c r="S13" s="246"/>
+      <c r="T13" s="246"/>
     </row>
     <row r="14" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A14" s="4"/>
+      <c r="B14" s="246"/>
+      <c r="C14" s="246"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
+      <c r="R14" s="246"/>
+      <c r="S14" s="246"/>
+      <c r="T14" s="246"/>
     </row>
     <row r="15" spans="1:20" customHeight="1" ht="39" s="246" customFormat="1">
       <c r="A15" s="4"/>
+      <c r="B15" s="246"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="246"/>
+      <c r="G15" s="246"/>
+      <c r="H15" s="246"/>
+      <c r="I15" s="246"/>
       <c r="J15" s="156" t="inlineStr">
         <is>
           <r>
@@ -6940,7 +7613,16 @@
           </r>
         </is>
       </c>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246"/>
+      <c r="M15" s="246"/>
+      <c r="N15" s="246"/>
+      <c r="O15" s="246"/>
+      <c r="P15" s="246"/>
       <c r="Q15" s="263"/>
+      <c r="R15" s="246"/>
+      <c r="S15" s="246"/>
+      <c r="T15" s="246"/>
     </row>
     <row r="16" spans="1:20" customHeight="1" ht="9" s="246" customFormat="1">
       <c r="A16" s="7"/>
@@ -6960,6 +7642,9 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="246"/>
+      <c r="S16" s="246"/>
+      <c r="T16" s="246"/>
     </row>
     <row r="17" spans="1:20" customHeight="1" ht="8.25" s="246" customFormat="1">
       <c r="A17" s="4"/>
@@ -6970,13 +7655,24 @@
           </r>
         </is>
       </c>
+      <c r="C17" s="246"/>
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
       <c r="I17" s="265"/>
       <c r="J17" s="265"/>
       <c r="K17" s="265"/>
       <c r="L17" s="265"/>
       <c r="M17" s="265"/>
       <c r="N17" s="265"/>
+      <c r="O17" s="246"/>
+      <c r="P17" s="246"/>
       <c r="Q17" s="5"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
     </row>
     <row r="18" spans="1:20" customHeight="1" ht="21.75" s="246" customFormat="1">
       <c r="A18" s="266" t="inlineStr">
@@ -6995,6 +7691,7 @@
       <c r="H18" s="255"/>
       <c r="I18" s="255"/>
       <c r="J18" s="256"/>
+      <c r="K18" s="246"/>
       <c r="L18" s="267" t="inlineStr">
         <is>
           <r>
@@ -7007,6 +7704,9 @@
       <c r="O18" s="255"/>
       <c r="P18" s="255"/>
       <c r="Q18" s="256"/>
+      <c r="R18" s="246"/>
+      <c r="S18" s="246"/>
+      <c r="T18" s="246"/>
     </row>
     <row r="19" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
@@ -7034,6 +7734,7 @@
       <c r="H19" s="251"/>
       <c r="I19" s="251"/>
       <c r="J19" s="252"/>
+      <c r="K19" s="246"/>
       <c r="L19" s="166" t="inlineStr">
         <is>
           <r>
@@ -7076,6 +7777,9 @@
           </r>
         </is>
       </c>
+      <c r="R19" s="246"/>
+      <c r="S19" s="246"/>
+      <c r="T19" s="246"/>
     </row>
     <row r="20" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
@@ -7100,6 +7804,7 @@
       <c r="H20" s="253"/>
       <c r="I20" s="253"/>
       <c r="J20" s="254"/>
+      <c r="K20" s="246"/>
       <c r="L20" s="167" t="inlineStr">
         <is>
           <r>
@@ -7142,6 +7847,9 @@
           </r>
         </is>
       </c>
+      <c r="R20" s="246"/>
+      <c r="S20" s="246"/>
+      <c r="T20" s="246"/>
     </row>
     <row r="21" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
@@ -7196,6 +7904,7 @@
           </r>
         </is>
       </c>
+      <c r="K21" s="246"/>
       <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
         <v>0</v>
@@ -7211,6 +7920,9 @@
       </c>
       <c r="P21" s="13"/>
       <c r="Q21" s="13"/>
+      <c r="R21" s="246"/>
+      <c r="S21" s="246"/>
+      <c r="T21" s="246"/>
     </row>
     <row r="22" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
@@ -7265,12 +7977,16 @@
           </r>
         </is>
       </c>
+      <c r="K22" s="246"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
+      <c r="R22" s="246"/>
+      <c r="S22" s="246"/>
+      <c r="T22" s="246"/>
     </row>
     <row r="23" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
@@ -7325,12 +8041,16 @@
           </r>
         </is>
       </c>
+      <c r="K23" s="246"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
+      <c r="R23" s="246"/>
+      <c r="S23" s="246"/>
+      <c r="T23" s="246"/>
     </row>
     <row r="24" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A24" s="269" t="inlineStr">
@@ -7364,12 +8084,16 @@
         </is>
       </c>
       <c r="J24" s="252"/>
+      <c r="K24" s="246"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
+      <c r="R24" s="246"/>
+      <c r="S24" s="246"/>
+      <c r="T24" s="246"/>
     </row>
     <row r="25" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A25" s="272"/>
@@ -7382,13 +8106,22 @@
       </c>
       <c r="C25" s="263"/>
       <c r="D25" s="272"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
       <c r="J25" s="263"/>
+      <c r="K25" s="246"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="246"/>
+      <c r="S25" s="246"/>
+      <c r="T25" s="246"/>
     </row>
     <row r="26" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A26" s="273"/>
@@ -7401,12 +8134,16 @@
       <c r="H26" s="253"/>
       <c r="I26" s="253"/>
       <c r="J26" s="254"/>
+      <c r="K26" s="246"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
+      <c r="R26" s="246"/>
+      <c r="S26" s="246"/>
+      <c r="T26" s="246"/>
     </row>
     <row r="27" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
@@ -7440,12 +8177,16 @@
       </c>
       <c r="I27" s="255"/>
       <c r="J27" s="256"/>
+      <c r="K27" s="246"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
+      <c r="R27" s="246"/>
+      <c r="S27" s="246"/>
+      <c r="T27" s="246"/>
     </row>
     <row r="28" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
@@ -7479,12 +8220,16 @@
         </is>
       </c>
       <c r="J28" s="252"/>
+      <c r="K28" s="246"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
+      <c r="R28" s="246"/>
+      <c r="S28" s="246"/>
+      <c r="T28" s="246"/>
     </row>
     <row r="29" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A29" s="275" t="inlineStr">
@@ -7494,15 +8239,25 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="246"/>
       <c r="C29" s="263"/>
       <c r="D29" s="272"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="246"/>
+      <c r="G29" s="246"/>
+      <c r="H29" s="246"/>
+      <c r="I29" s="246"/>
       <c r="J29" s="263"/>
+      <c r="K29" s="246"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
+      <c r="R29" s="246"/>
+      <c r="S29" s="246"/>
+      <c r="T29" s="246"/>
     </row>
     <row r="30" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A30" s="276" t="inlineStr">
@@ -7521,12 +8276,16 @@
       <c r="H30" s="253"/>
       <c r="I30" s="253"/>
       <c r="J30" s="254"/>
+      <c r="K30" s="246"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
+      <c r="R30" s="246"/>
+      <c r="S30" s="246"/>
+      <c r="T30" s="246"/>
     </row>
     <row r="31" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
@@ -7563,12 +8322,16 @@
       </c>
       <c r="I31" s="255"/>
       <c r="J31" s="256"/>
+      <c r="K31" s="246"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
+      <c r="R31" s="246"/>
+      <c r="S31" s="246"/>
+      <c r="T31" s="246"/>
     </row>
     <row r="32" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
@@ -7617,12 +8380,16 @@
         </is>
       </c>
       <c r="J32" s="256"/>
+      <c r="K32" s="246"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
+      <c r="R32" s="246"/>
+      <c r="S32" s="246"/>
+      <c r="T32" s="246"/>
     </row>
     <row r="33" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
@@ -7665,12 +8432,16 @@
         </is>
       </c>
       <c r="J33" s="256"/>
+      <c r="K33" s="246"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
+      <c r="R33" s="246"/>
+      <c r="S33" s="246"/>
+      <c r="T33" s="246"/>
     </row>
     <row r="34" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A34" s="278" t="inlineStr">
@@ -7689,32 +8460,60 @@
       <c r="H34" s="251"/>
       <c r="I34" s="251"/>
       <c r="J34" s="252"/>
+      <c r="K34" s="246"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
+      <c r="R34" s="246"/>
+      <c r="S34" s="246"/>
+      <c r="T34" s="246"/>
     </row>
     <row r="35" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A35" s="272"/>
+      <c r="B35" s="246"/>
+      <c r="C35" s="246"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
+      <c r="G35" s="246"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
       <c r="J35" s="263"/>
+      <c r="K35" s="246"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
+      <c r="R35" s="246"/>
+      <c r="S35" s="246"/>
+      <c r="T35" s="246"/>
     </row>
     <row r="36" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A36" s="272"/>
+      <c r="B36" s="246"/>
+      <c r="C36" s="246"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
+      <c r="G36" s="246"/>
+      <c r="H36" s="246"/>
+      <c r="I36" s="246"/>
       <c r="J36" s="263"/>
+      <c r="K36" s="246"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
+      <c r="R36" s="246"/>
+      <c r="S36" s="246"/>
+      <c r="T36" s="246"/>
     </row>
     <row r="37" spans="1:20" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A37" s="273"/>
@@ -7727,12 +8526,16 @@
       <c r="H37" s="253"/>
       <c r="I37" s="253"/>
       <c r="J37" s="254"/>
+      <c r="K37" s="246"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
+      <c r="R37" s="246"/>
+      <c r="S37" s="246"/>
+      <c r="T37" s="246"/>
     </row>
     <row r="38" spans="1:20" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A38" s="173" t="inlineStr">
@@ -7751,6 +8554,7 @@
       <c r="H38" s="255"/>
       <c r="I38" s="255"/>
       <c r="J38" s="256"/>
+      <c r="K38" s="246"/>
       <c r="L38" s="279" t="inlineStr">
         <is>
           <r>
@@ -7763,6 +8567,9 @@
       <c r="O38" s="251"/>
       <c r="P38" s="251"/>
       <c r="Q38" s="252"/>
+      <c r="R38" s="246"/>
+      <c r="S38" s="246"/>
+      <c r="T38" s="246"/>
     </row>
     <row r="39" spans="1:20" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A39" s="280" t="inlineStr">
@@ -7793,6 +8600,7 @@
       </c>
       <c r="I39" s="255"/>
       <c r="J39" s="256"/>
+      <c r="K39" s="246"/>
       <c r="L39" s="281" t="inlineStr">
         <is>
           <r>
@@ -7805,6 +8613,9 @@
       <c r="O39" s="251"/>
       <c r="P39" s="251"/>
       <c r="Q39" s="252"/>
+      <c r="R39" s="246"/>
+      <c r="S39" s="246"/>
+      <c r="T39" s="246"/>
     </row>
     <row r="40" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
@@ -7841,8 +8652,16 @@
       </c>
       <c r="I40" s="255"/>
       <c r="J40" s="256"/>
+      <c r="K40" s="246"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="246"/>
+      <c r="N40" s="246"/>
+      <c r="O40" s="246"/>
+      <c r="P40" s="246"/>
       <c r="Q40" s="5"/>
+      <c r="R40" s="246"/>
+      <c r="S40" s="246"/>
+      <c r="T40" s="246"/>
     </row>
     <row r="41" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
@@ -7879,7 +8698,10 @@
       </c>
       <c r="I41" s="255"/>
       <c r="J41" s="256"/>
+      <c r="K41" s="246"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="246"/>
+      <c r="N41" s="246"/>
       <c r="O41" s="246" t="inlineStr">
         <is>
           <r>
@@ -7887,7 +8709,11 @@
           </r>
         </is>
       </c>
+      <c r="P41" s="246"/>
       <c r="Q41" s="5"/>
+      <c r="R41" s="246"/>
+      <c r="S41" s="246"/>
+      <c r="T41" s="246"/>
     </row>
     <row r="42" spans="1:20" customHeight="1" ht="33" s="246" customFormat="1">
       <c r="A42" s="267" t="inlineStr">
@@ -7907,8 +8733,16 @@
       <c r="H42" s="255"/>
       <c r="I42" s="255"/>
       <c r="J42" s="256"/>
+      <c r="K42" s="246"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="246"/>
+      <c r="N42" s="246"/>
+      <c r="O42" s="246"/>
+      <c r="P42" s="246"/>
       <c r="Q42" s="5"/>
+      <c r="R42" s="246"/>
+      <c r="S42" s="246"/>
+      <c r="T42" s="246"/>
     </row>
     <row r="43" spans="1:20" customHeight="1" ht="22.5" s="246" customFormat="1">
       <c r="A43" s="282" t="inlineStr">
@@ -7933,8 +8767,16 @@
       </c>
       <c r="I43" s="255"/>
       <c r="J43" s="256"/>
+      <c r="K43" s="246"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="246"/>
+      <c r="N43" s="246"/>
+      <c r="O43" s="246"/>
+      <c r="P43" s="246"/>
       <c r="Q43" s="5"/>
+      <c r="R43" s="246"/>
+      <c r="S43" s="246"/>
+      <c r="T43" s="246"/>
     </row>
     <row r="44" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
@@ -7959,8 +8801,16 @@
       </c>
       <c r="I44" s="255"/>
       <c r="J44" s="256"/>
+      <c r="K44" s="246"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="246"/>
+      <c r="N44" s="246"/>
+      <c r="O44" s="246"/>
+      <c r="P44" s="246"/>
       <c r="Q44" s="5"/>
+      <c r="R44" s="246"/>
+      <c r="S44" s="246"/>
+      <c r="T44" s="246"/>
     </row>
     <row r="45" spans="1:20" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
@@ -7992,9 +8842,39 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="1:20" customHeight="1" ht="6" s="246" customFormat="1"/>
+      <c r="R45" s="246"/>
+      <c r="S45" s="246"/>
+      <c r="T45" s="246"/>
+    </row>
+    <row r="46" spans="1:20" customHeight="1" ht="6" s="246" customFormat="1">
+      <c r="A46" s="246"/>
+      <c r="B46" s="246"/>
+      <c r="C46" s="246"/>
+      <c r="D46" s="246"/>
+      <c r="E46" s="246"/>
+      <c r="F46" s="246"/>
+      <c r="G46" s="246"/>
+      <c r="H46" s="246"/>
+      <c r="I46" s="246"/>
+      <c r="J46" s="246"/>
+      <c r="K46" s="246"/>
+      <c r="L46" s="246"/>
+      <c r="M46" s="246"/>
+      <c r="N46" s="246"/>
+      <c r="O46" s="246"/>
+      <c r="P46" s="246"/>
+      <c r="Q46" s="246"/>
+      <c r="R46" s="246"/>
+      <c r="S46" s="246"/>
+      <c r="T46" s="246"/>
+    </row>
     <row r="47" spans="1:20" customHeight="1" ht="23.25" s="246" customFormat="1">
+      <c r="A47" s="246"/>
+      <c r="B47" s="246"/>
+      <c r="C47" s="246"/>
+      <c r="D47" s="246"/>
+      <c r="E47" s="246"/>
+      <c r="F47" s="246"/>
       <c r="G47" s="163" t="inlineStr">
         <is>
           <r>
@@ -8002,6 +8882,12 @@
           </r>
         </is>
       </c>
+      <c r="H47" s="246"/>
+      <c r="I47" s="246"/>
+      <c r="J47" s="246"/>
+      <c r="K47" s="246"/>
+      <c r="L47" s="246"/>
+      <c r="M47" s="246"/>
       <c r="N47" s="164" t="inlineStr">
         <is>
           <r>
@@ -8009,6 +8895,12 @@
           </r>
         </is>
       </c>
+      <c r="O47" s="246"/>
+      <c r="P47" s="246"/>
+      <c r="Q47" s="246"/>
+      <c r="R47" s="246"/>
+      <c r="S47" s="246"/>
+      <c r="T47" s="246"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -8174,6 +9066,12 @@
           </r>
         </is>
       </c>
+      <c r="R1"/>
+      <c r="S1"/>
+      <c r="T1"/>
+      <c r="U1"/>
+      <c r="V1"/>
+      <c r="W1"/>
     </row>
     <row r="2" spans="1:23" customHeight="1" ht="60" s="246" customFormat="1">
       <c r="A2" s="283" t="inlineStr">
@@ -8199,6 +9097,12 @@
       <c r="O2" s="251"/>
       <c r="P2" s="251"/>
       <c r="Q2" s="252"/>
+      <c r="R2" s="246"/>
+      <c r="S2" s="246"/>
+      <c r="T2" s="246"/>
+      <c r="U2" s="246"/>
+      <c r="V2" s="246"/>
+      <c r="W2" s="246"/>
     </row>
     <row r="3" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A3" s="1"/>
@@ -8248,6 +9152,12 @@
       </c>
       <c r="P3" s="253"/>
       <c r="Q3" s="254"/>
+      <c r="R3" s="246"/>
+      <c r="S3" s="246"/>
+      <c r="T3" s="246"/>
+      <c r="U3" s="246"/>
+      <c r="V3" s="246"/>
+      <c r="W3" s="246"/>
     </row>
     <row r="4" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A4" s="173" t="inlineStr">
@@ -8297,6 +9207,12 @@
         </is>
       </c>
       <c r="Q4" s="256"/>
+      <c r="R4" s="246"/>
+      <c r="S4" s="246"/>
+      <c r="T4" s="246"/>
+      <c r="U4" s="246"/>
+      <c r="V4" s="246"/>
+      <c r="W4" s="246"/>
     </row>
     <row r="5" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A5" s="173" t="inlineStr">
@@ -8337,6 +9253,7 @@
         <v>0</v>
       </c>
       <c r="Q5" s="256"/>
+      <c r="R5" s="246"/>
       <c r="S5" s="246" t="inlineStr">
         <is>
           <r>
@@ -8344,6 +9261,10 @@
           </r>
         </is>
       </c>
+      <c r="T5" s="246"/>
+      <c r="U5" s="246"/>
+      <c r="V5" s="246"/>
+      <c r="W5" s="246"/>
     </row>
     <row r="6" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A6" s="173" t="inlineStr">
@@ -8381,6 +9302,7 @@
       <c r="O6" s="255"/>
       <c r="P6" s="255"/>
       <c r="Q6" s="256"/>
+      <c r="R6" s="246"/>
       <c r="S6" s="284" t="inlineStr">
         <is>
           <r>
@@ -8388,6 +9310,10 @@
           </r>
         </is>
       </c>
+      <c r="T6" s="246"/>
+      <c r="U6" s="246"/>
+      <c r="V6" s="246"/>
+      <c r="W6" s="246"/>
     </row>
     <row r="7" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A7" s="173" t="inlineStr">
@@ -8415,6 +9341,12 @@
       <c r="O7" s="255"/>
       <c r="P7" s="255"/>
       <c r="Q7" s="256"/>
+      <c r="R7" s="246"/>
+      <c r="S7" s="246"/>
+      <c r="T7" s="246"/>
+      <c r="U7" s="246"/>
+      <c r="V7" s="246"/>
+      <c r="W7" s="246"/>
     </row>
     <row r="8" spans="1:23" customHeight="1" ht="30" s="246" customFormat="1">
       <c r="A8" s="259" t="inlineStr">
@@ -8467,6 +9399,11 @@
           </r>
         </is>
       </c>
+      <c r="S8" s="246"/>
+      <c r="T8" s="246"/>
+      <c r="U8" s="246"/>
+      <c r="V8" s="246"/>
+      <c r="W8" s="246"/>
     </row>
     <row r="9" spans="1:23" customHeight="1" ht="6.75" s="246" customFormat="1">
       <c r="A9" s="1"/>
@@ -8486,6 +9423,12 @@
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="3"/>
+      <c r="R9" s="246"/>
+      <c r="S9" s="246"/>
+      <c r="T9" s="246"/>
+      <c r="U9" s="246"/>
+      <c r="V9" s="246"/>
+      <c r="W9" s="246"/>
     </row>
     <row r="10" spans="1:23" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A10" s="285" t="inlineStr">
@@ -8495,7 +9438,28 @@
           </r>
         </is>
       </c>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
+      <c r="D10" s="246"/>
+      <c r="E10" s="246"/>
+      <c r="F10" s="246"/>
+      <c r="G10" s="246"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
+      <c r="L10" s="246"/>
+      <c r="M10" s="246"/>
+      <c r="N10" s="246"/>
+      <c r="O10" s="246"/>
+      <c r="P10" s="246"/>
       <c r="Q10" s="263"/>
+      <c r="R10" s="246"/>
+      <c r="S10" s="246"/>
+      <c r="T10" s="246"/>
+      <c r="U10" s="246"/>
+      <c r="V10" s="246"/>
+      <c r="W10" s="246"/>
     </row>
     <row r="11" spans="1:23" customHeight="1" ht="22.5" s="246" customFormat="1">
       <c r="A11" s="1"/>
@@ -8506,7 +9470,27 @@
           </r>
         </is>
       </c>
+      <c r="C11" s="246"/>
+      <c r="D11" s="246"/>
+      <c r="E11" s="246"/>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
+      <c r="L11" s="246"/>
+      <c r="M11" s="246"/>
+      <c r="N11" s="246"/>
+      <c r="O11" s="246"/>
+      <c r="P11" s="246"/>
       <c r="Q11" s="263"/>
+      <c r="R11" s="246"/>
+      <c r="S11" s="246"/>
+      <c r="T11" s="246"/>
+      <c r="U11" s="246"/>
+      <c r="V11" s="246"/>
+      <c r="W11" s="246"/>
     </row>
     <row r="12" spans="1:23" customHeight="1" ht="20.25" s="246" customFormat="1">
       <c r="A12" s="1"/>
@@ -8532,6 +9516,12 @@
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="3"/>
+      <c r="R12" s="246"/>
+      <c r="S12" s="246"/>
+      <c r="T12" s="246"/>
+      <c r="U12" s="246"/>
+      <c r="V12" s="246"/>
+      <c r="W12" s="246"/>
     </row>
     <row r="13" spans="1:23" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A13" s="4" t="inlineStr">
@@ -8548,6 +9538,13 @@
           </r>
         </is>
       </c>
+      <c r="C13" s="246"/>
+      <c r="D13" s="246"/>
+      <c r="E13" s="246"/>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
       <c r="J13" s="246" t="inlineStr">
         <is>
           <r>
@@ -8555,25 +9552,58 @@
           </r>
         </is>
       </c>
+      <c r="K13" s="246"/>
       <c r="L13" s="169" t="str">
         <f>구매리스트!I3</f>
         <v>0</v>
       </c>
+      <c r="M13" s="246"/>
+      <c r="N13" s="246"/>
       <c r="O13" s="246"/>
       <c r="P13" s="264"/>
       <c r="Q13" s="5"/>
+      <c r="R13" s="246"/>
       <c r="S13" s="72"/>
+      <c r="T13" s="246"/>
+      <c r="U13" s="246"/>
+      <c r="V13" s="246"/>
+      <c r="W13" s="246"/>
     </row>
     <row r="14" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A14" s="4"/>
+      <c r="B14" s="246"/>
+      <c r="C14" s="246"/>
+      <c r="D14" s="246"/>
+      <c r="E14" s="246"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
+      <c r="L14" s="246"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="5"/>
+      <c r="R14" s="246"/>
+      <c r="S14" s="246"/>
+      <c r="T14" s="246"/>
+      <c r="U14" s="246"/>
+      <c r="V14" s="246"/>
+      <c r="W14" s="246"/>
     </row>
     <row r="15" spans="1:23" customHeight="1" ht="39" s="246" customFormat="1">
       <c r="A15" s="4"/>
+      <c r="B15" s="246"/>
+      <c r="C15" s="246"/>
+      <c r="D15" s="246"/>
+      <c r="E15" s="246"/>
+      <c r="F15" s="246"/>
+      <c r="G15" s="246"/>
+      <c r="H15" s="246"/>
+      <c r="I15" s="246"/>
       <c r="J15" s="156" t="inlineStr">
         <is>
           <r>
@@ -8581,7 +9611,18 @@
           </r>
         </is>
       </c>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246"/>
+      <c r="M15" s="246"/>
+      <c r="N15" s="246"/>
+      <c r="O15" s="246"/>
+      <c r="P15" s="246"/>
       <c r="Q15" s="263"/>
+      <c r="R15" s="246"/>
+      <c r="S15" s="246"/>
+      <c r="T15" s="246"/>
+      <c r="U15" s="246"/>
+      <c r="V15" s="246"/>
       <c r="W15" s="246" t="inlineStr">
         <is>
           <r>
@@ -8608,6 +9649,12 @@
       <c r="O16" s="8"/>
       <c r="P16" s="8"/>
       <c r="Q16" s="9"/>
+      <c r="R16" s="246"/>
+      <c r="S16" s="246"/>
+      <c r="T16" s="246"/>
+      <c r="U16" s="246"/>
+      <c r="V16" s="246"/>
+      <c r="W16" s="246"/>
     </row>
     <row r="17" spans="1:23" customHeight="1" ht="8.25" s="246" customFormat="1">
       <c r="A17" s="4"/>
@@ -8618,13 +9665,27 @@
           </r>
         </is>
       </c>
+      <c r="C17" s="246"/>
+      <c r="D17" s="246"/>
+      <c r="E17" s="246"/>
+      <c r="F17" s="246"/>
+      <c r="G17" s="246"/>
+      <c r="H17" s="246"/>
       <c r="I17" s="265"/>
       <c r="J17" s="265"/>
       <c r="K17" s="265"/>
       <c r="L17" s="265"/>
       <c r="M17" s="265"/>
       <c r="N17" s="265"/>
+      <c r="O17" s="246"/>
+      <c r="P17" s="246"/>
       <c r="Q17" s="5"/>
+      <c r="R17" s="246"/>
+      <c r="S17" s="246"/>
+      <c r="T17" s="246"/>
+      <c r="U17" s="246"/>
+      <c r="V17" s="246"/>
+      <c r="W17" s="246"/>
     </row>
     <row r="18" spans="1:23" customHeight="1" ht="21.75" s="246" customFormat="1">
       <c r="A18" s="266" t="inlineStr">
@@ -8643,6 +9704,7 @@
       <c r="H18" s="255"/>
       <c r="I18" s="255"/>
       <c r="J18" s="256"/>
+      <c r="K18" s="246"/>
       <c r="L18" s="267" t="inlineStr">
         <is>
           <r>
@@ -8655,6 +9717,12 @@
       <c r="O18" s="255"/>
       <c r="P18" s="255"/>
       <c r="Q18" s="256"/>
+      <c r="R18" s="246"/>
+      <c r="S18" s="246"/>
+      <c r="T18" s="246"/>
+      <c r="U18" s="246"/>
+      <c r="V18" s="246"/>
+      <c r="W18" s="246"/>
     </row>
     <row r="19" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A19" s="60" t="inlineStr">
@@ -8682,6 +9750,7 @@
       <c r="H19" s="251"/>
       <c r="I19" s="251"/>
       <c r="J19" s="252"/>
+      <c r="K19" s="246"/>
       <c r="L19" s="286" t="inlineStr">
         <is>
           <r>
@@ -8728,6 +9797,12 @@
           </r>
         </is>
       </c>
+      <c r="R19" s="246"/>
+      <c r="S19" s="246"/>
+      <c r="T19" s="246"/>
+      <c r="U19" s="246"/>
+      <c r="V19" s="246"/>
+      <c r="W19" s="246"/>
     </row>
     <row r="20" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A20" s="58" t="inlineStr">
@@ -8752,12 +9827,19 @@
       <c r="H20" s="253"/>
       <c r="I20" s="253"/>
       <c r="J20" s="254"/>
+      <c r="K20" s="246"/>
       <c r="L20" s="291"/>
       <c r="M20" s="291"/>
       <c r="N20" s="291"/>
       <c r="O20" s="291"/>
       <c r="P20" s="291"/>
       <c r="Q20" s="291"/>
+      <c r="R20" s="246"/>
+      <c r="S20" s="246"/>
+      <c r="T20" s="246"/>
+      <c r="U20" s="246"/>
+      <c r="V20" s="246"/>
+      <c r="W20" s="246"/>
     </row>
     <row r="21" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A21" s="62" t="inlineStr">
@@ -8812,6 +9894,7 @@
           </r>
         </is>
       </c>
+      <c r="K21" s="246"/>
       <c r="L21" s="121" t="str">
         <f>구매리스트!I10</f>
         <v>0</v>
@@ -8834,6 +9917,11 @@
           </r>
         </is>
       </c>
+      <c r="S21" s="246"/>
+      <c r="T21" s="246"/>
+      <c r="U21" s="246"/>
+      <c r="V21" s="246"/>
+      <c r="W21" s="246"/>
     </row>
     <row r="22" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A22" s="63" t="inlineStr">
@@ -8888,12 +9976,14 @@
           </r>
         </is>
       </c>
+      <c r="K22" s="246"/>
       <c r="L22" s="14"/>
       <c r="M22" s="14"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
       <c r="Q22" s="14"/>
+      <c r="R22" s="246"/>
       <c r="S22" s="246" t="inlineStr">
         <is>
           <r>
@@ -8901,6 +9991,10 @@
           </r>
         </is>
       </c>
+      <c r="T22" s="246"/>
+      <c r="U22" s="246"/>
+      <c r="V22" s="246"/>
+      <c r="W22" s="246"/>
     </row>
     <row r="23" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A23" s="63" t="inlineStr">
@@ -8955,12 +10049,19 @@
           </r>
         </is>
       </c>
+      <c r="K23" s="246"/>
       <c r="L23" s="14"/>
       <c r="M23" s="14"/>
       <c r="N23" s="14"/>
       <c r="O23" s="14"/>
       <c r="P23" s="14"/>
       <c r="Q23" s="14"/>
+      <c r="R23" s="246"/>
+      <c r="S23" s="246"/>
+      <c r="T23" s="246"/>
+      <c r="U23" s="246"/>
+      <c r="V23" s="246"/>
+      <c r="W23" s="246"/>
     </row>
     <row r="24" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A24" s="269" t="inlineStr">
@@ -8994,12 +10095,14 @@
         </is>
       </c>
       <c r="J24" s="252"/>
+      <c r="K24" s="246"/>
       <c r="L24" s="14"/>
       <c r="M24" s="14"/>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
+      <c r="R24" s="246"/>
       <c r="S24" s="246" t="inlineStr">
         <is>
           <r>
@@ -9007,6 +10110,10 @@
           </r>
         </is>
       </c>
+      <c r="T24" s="246"/>
+      <c r="U24" s="246"/>
+      <c r="V24" s="246"/>
+      <c r="W24" s="246"/>
     </row>
     <row r="25" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A25" s="272"/>
@@ -9020,13 +10127,25 @@
       </c>
       <c r="C25" s="263"/>
       <c r="D25" s="272"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
+      <c r="G25" s="246"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
       <c r="J25" s="263"/>
+      <c r="K25" s="246"/>
       <c r="L25" s="15"/>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
       <c r="O25" s="15"/>
       <c r="P25" s="15"/>
       <c r="Q25" s="15"/>
+      <c r="R25" s="246"/>
+      <c r="S25" s="246"/>
+      <c r="T25" s="246"/>
+      <c r="U25" s="246"/>
+      <c r="V25" s="246"/>
+      <c r="W25" s="246"/>
     </row>
     <row r="26" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A26" s="273"/>
@@ -9039,12 +10158,14 @@
       <c r="H26" s="253"/>
       <c r="I26" s="253"/>
       <c r="J26" s="254"/>
+      <c r="K26" s="246"/>
       <c r="L26" s="68"/>
       <c r="M26" s="68"/>
       <c r="N26" s="68"/>
       <c r="O26" s="68"/>
       <c r="P26" s="68"/>
       <c r="Q26" s="68"/>
+      <c r="R26" s="246"/>
       <c r="S26" s="246" t="inlineStr">
         <is>
           <r>
@@ -9052,6 +10173,10 @@
           </r>
         </is>
       </c>
+      <c r="T26" s="246"/>
+      <c r="U26" s="246"/>
+      <c r="V26" s="246"/>
+      <c r="W26" s="246"/>
     </row>
     <row r="27" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A27" s="63" t="inlineStr">
@@ -9085,12 +10210,19 @@
       </c>
       <c r="I27" s="255"/>
       <c r="J27" s="256"/>
+      <c r="K27" s="246"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
       <c r="N27" s="14"/>
       <c r="O27" s="14"/>
       <c r="P27" s="14"/>
       <c r="Q27" s="14"/>
+      <c r="R27" s="246"/>
+      <c r="S27" s="246"/>
+      <c r="T27" s="246"/>
+      <c r="U27" s="246"/>
+      <c r="V27" s="246"/>
+      <c r="W27" s="246"/>
     </row>
     <row r="28" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A28" s="64" t="inlineStr">
@@ -9125,12 +10257,19 @@
         </is>
       </c>
       <c r="J28" s="252"/>
+      <c r="K28" s="246"/>
       <c r="L28" s="14"/>
       <c r="M28" s="14"/>
       <c r="N28" s="14"/>
       <c r="O28" s="14"/>
       <c r="P28" s="14"/>
       <c r="Q28" s="14"/>
+      <c r="R28" s="246"/>
+      <c r="S28" s="246"/>
+      <c r="T28" s="246"/>
+      <c r="U28" s="246"/>
+      <c r="V28" s="246"/>
+      <c r="W28" s="246"/>
     </row>
     <row r="29" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A29" s="293" t="inlineStr">
@@ -9140,15 +10279,28 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="246"/>
       <c r="C29" s="263"/>
       <c r="D29" s="272"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="246"/>
+      <c r="G29" s="246"/>
+      <c r="H29" s="246"/>
+      <c r="I29" s="246"/>
       <c r="J29" s="263"/>
+      <c r="K29" s="246"/>
       <c r="L29" s="14"/>
       <c r="M29" s="14"/>
       <c r="N29" s="14"/>
       <c r="O29" s="14"/>
       <c r="P29" s="14"/>
       <c r="Q29" s="14"/>
+      <c r="R29" s="246"/>
+      <c r="S29" s="246"/>
+      <c r="T29" s="246"/>
+      <c r="U29" s="246"/>
+      <c r="V29" s="246"/>
+      <c r="W29" s="246"/>
     </row>
     <row r="30" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A30" s="294" t="inlineStr">
@@ -9167,12 +10319,19 @@
       <c r="H30" s="253"/>
       <c r="I30" s="253"/>
       <c r="J30" s="254"/>
+      <c r="K30" s="246"/>
       <c r="L30" s="15"/>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
       <c r="O30" s="15"/>
       <c r="P30" s="15"/>
       <c r="Q30" s="15"/>
+      <c r="R30" s="246"/>
+      <c r="S30" s="246"/>
+      <c r="T30" s="246"/>
+      <c r="U30" s="246"/>
+      <c r="V30" s="246"/>
+      <c r="W30" s="246"/>
     </row>
     <row r="31" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A31" s="65" t="inlineStr">
@@ -9210,12 +10369,19 @@
       </c>
       <c r="I31" s="255"/>
       <c r="J31" s="256"/>
+      <c r="K31" s="246"/>
       <c r="L31" s="14"/>
       <c r="M31" s="14"/>
       <c r="N31" s="14"/>
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="14"/>
+      <c r="R31" s="246"/>
+      <c r="S31" s="246"/>
+      <c r="T31" s="246"/>
+      <c r="U31" s="246"/>
+      <c r="V31" s="246"/>
+      <c r="W31" s="246"/>
     </row>
     <row r="32" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A32" s="66" t="inlineStr">
@@ -9265,12 +10431,19 @@
         </is>
       </c>
       <c r="J32" s="256"/>
+      <c r="K32" s="246"/>
       <c r="L32" s="14"/>
       <c r="M32" s="14"/>
       <c r="N32" s="14"/>
       <c r="O32" s="14"/>
       <c r="P32" s="14"/>
       <c r="Q32" s="14"/>
+      <c r="R32" s="246"/>
+      <c r="S32" s="246"/>
+      <c r="T32" s="246"/>
+      <c r="U32" s="246"/>
+      <c r="V32" s="246"/>
+      <c r="W32" s="246"/>
     </row>
     <row r="33" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A33" s="66" t="inlineStr">
@@ -9314,12 +10487,19 @@
         </is>
       </c>
       <c r="J33" s="256"/>
+      <c r="K33" s="246"/>
       <c r="L33" s="14"/>
       <c r="M33" s="14"/>
       <c r="N33" s="14"/>
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="14"/>
+      <c r="R33" s="246"/>
+      <c r="S33" s="246"/>
+      <c r="T33" s="246"/>
+      <c r="U33" s="246"/>
+      <c r="V33" s="246"/>
+      <c r="W33" s="246"/>
     </row>
     <row r="34" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A34" s="278" t="inlineStr">
@@ -9338,32 +10518,69 @@
       <c r="H34" s="251"/>
       <c r="I34" s="251"/>
       <c r="J34" s="252"/>
+      <c r="K34" s="246"/>
       <c r="L34" s="14"/>
       <c r="M34" s="14"/>
       <c r="N34" s="14"/>
       <c r="O34" s="14"/>
       <c r="P34" s="14"/>
       <c r="Q34" s="14"/>
+      <c r="R34" s="246"/>
+      <c r="S34" s="246"/>
+      <c r="T34" s="246"/>
+      <c r="U34" s="246"/>
+      <c r="V34" s="246"/>
+      <c r="W34" s="246"/>
     </row>
     <row r="35" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A35" s="272"/>
+      <c r="B35" s="246"/>
+      <c r="C35" s="246"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
+      <c r="G35" s="246"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
       <c r="J35" s="263"/>
+      <c r="K35" s="246"/>
       <c r="L35" s="14"/>
       <c r="M35" s="14"/>
       <c r="N35" s="14"/>
       <c r="O35" s="14"/>
       <c r="P35" s="14"/>
       <c r="Q35" s="14"/>
+      <c r="R35" s="246"/>
+      <c r="S35" s="246"/>
+      <c r="T35" s="246"/>
+      <c r="U35" s="246"/>
+      <c r="V35" s="246"/>
+      <c r="W35" s="246"/>
     </row>
     <row r="36" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A36" s="272"/>
+      <c r="B36" s="246"/>
+      <c r="C36" s="246"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
+      <c r="G36" s="246"/>
+      <c r="H36" s="246"/>
+      <c r="I36" s="246"/>
       <c r="J36" s="263"/>
+      <c r="K36" s="246"/>
       <c r="L36" s="14"/>
       <c r="M36" s="14"/>
       <c r="N36" s="14"/>
       <c r="O36" s="14"/>
       <c r="P36" s="14"/>
       <c r="Q36" s="14"/>
+      <c r="R36" s="246"/>
+      <c r="S36" s="246"/>
+      <c r="T36" s="246"/>
+      <c r="U36" s="246"/>
+      <c r="V36" s="246"/>
+      <c r="W36" s="246"/>
     </row>
     <row r="37" spans="1:23" customHeight="1" ht="20.45" s="246" customFormat="1">
       <c r="A37" s="273"/>
@@ -9376,12 +10593,19 @@
       <c r="H37" s="253"/>
       <c r="I37" s="253"/>
       <c r="J37" s="254"/>
+      <c r="K37" s="246"/>
       <c r="L37" s="15"/>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
       <c r="O37" s="15"/>
       <c r="P37" s="15"/>
       <c r="Q37" s="15"/>
+      <c r="R37" s="246"/>
+      <c r="S37" s="246"/>
+      <c r="T37" s="246"/>
+      <c r="U37" s="246"/>
+      <c r="V37" s="246"/>
+      <c r="W37" s="246"/>
     </row>
     <row r="38" spans="1:23" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A38" s="173" t="inlineStr">
@@ -9400,6 +10624,7 @@
       <c r="H38" s="255"/>
       <c r="I38" s="255"/>
       <c r="J38" s="256"/>
+      <c r="K38" s="246"/>
       <c r="L38" s="297" t="inlineStr">
         <is>
           <r>
@@ -9412,6 +10637,12 @@
       <c r="O38" s="251"/>
       <c r="P38" s="251"/>
       <c r="Q38" s="252"/>
+      <c r="R38" s="246"/>
+      <c r="S38" s="246"/>
+      <c r="T38" s="246"/>
+      <c r="U38" s="246"/>
+      <c r="V38" s="246"/>
+      <c r="W38" s="246"/>
     </row>
     <row r="39" spans="1:23" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A39" s="280" t="inlineStr">
@@ -9443,6 +10674,7 @@
       </c>
       <c r="I39" s="255"/>
       <c r="J39" s="256"/>
+      <c r="K39" s="246"/>
       <c r="L39" s="300" t="inlineStr">
         <is>
           <r>
@@ -9455,6 +10687,12 @@
       <c r="O39" s="251"/>
       <c r="P39" s="251"/>
       <c r="Q39" s="252"/>
+      <c r="R39" s="246"/>
+      <c r="S39" s="246"/>
+      <c r="T39" s="246"/>
+      <c r="U39" s="246"/>
+      <c r="V39" s="246"/>
+      <c r="W39" s="246"/>
     </row>
     <row r="40" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A40" s="136" t="inlineStr">
@@ -9491,8 +10729,19 @@
       </c>
       <c r="I40" s="255"/>
       <c r="J40" s="256"/>
+      <c r="K40" s="246"/>
       <c r="L40" s="4"/>
+      <c r="M40" s="246"/>
+      <c r="N40" s="246"/>
+      <c r="O40" s="246"/>
+      <c r="P40" s="246"/>
       <c r="Q40" s="5"/>
+      <c r="R40" s="246"/>
+      <c r="S40" s="246"/>
+      <c r="T40" s="246"/>
+      <c r="U40" s="246"/>
+      <c r="V40" s="246"/>
+      <c r="W40" s="246"/>
     </row>
     <row r="41" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A41" s="136" t="inlineStr">
@@ -9529,7 +10778,10 @@
       </c>
       <c r="I41" s="255"/>
       <c r="J41" s="256"/>
+      <c r="K41" s="246"/>
       <c r="L41" s="4"/>
+      <c r="M41" s="246"/>
+      <c r="N41" s="246"/>
       <c r="O41" s="246" t="inlineStr">
         <is>
           <r>
@@ -9537,7 +10789,14 @@
           </r>
         </is>
       </c>
+      <c r="P41" s="246"/>
       <c r="Q41" s="5"/>
+      <c r="R41" s="246"/>
+      <c r="S41" s="246"/>
+      <c r="T41" s="246"/>
+      <c r="U41" s="246"/>
+      <c r="V41" s="246"/>
+      <c r="W41" s="246"/>
     </row>
     <row r="42" spans="1:23" customHeight="1" ht="33" s="246" customFormat="1">
       <c r="A42" s="298" t="inlineStr">
@@ -9556,8 +10815,19 @@
       <c r="H42" s="255"/>
       <c r="I42" s="255"/>
       <c r="J42" s="256"/>
+      <c r="K42" s="246"/>
       <c r="L42" s="4"/>
+      <c r="M42" s="246"/>
+      <c r="N42" s="246"/>
+      <c r="O42" s="246"/>
+      <c r="P42" s="246"/>
       <c r="Q42" s="5"/>
+      <c r="R42" s="246"/>
+      <c r="S42" s="246"/>
+      <c r="T42" s="246"/>
+      <c r="U42" s="246"/>
+      <c r="V42" s="246"/>
+      <c r="W42" s="246"/>
     </row>
     <row r="43" spans="1:23" customHeight="1" ht="22.5" s="246" customFormat="1">
       <c r="A43" s="301" t="inlineStr">
@@ -9582,8 +10852,19 @@
       </c>
       <c r="I43" s="255"/>
       <c r="J43" s="256"/>
+      <c r="K43" s="246"/>
       <c r="L43" s="4"/>
+      <c r="M43" s="246"/>
+      <c r="N43" s="246"/>
+      <c r="O43" s="246"/>
+      <c r="P43" s="246"/>
       <c r="Q43" s="5"/>
+      <c r="R43" s="246"/>
+      <c r="S43" s="246"/>
+      <c r="T43" s="246"/>
+      <c r="U43" s="246"/>
+      <c r="V43" s="246"/>
+      <c r="W43" s="246"/>
     </row>
     <row r="44" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A44" s="136" t="inlineStr">
@@ -9608,8 +10889,19 @@
       </c>
       <c r="I44" s="255"/>
       <c r="J44" s="256"/>
+      <c r="K44" s="246"/>
       <c r="L44" s="4"/>
+      <c r="M44" s="246"/>
+      <c r="N44" s="246"/>
+      <c r="O44" s="246"/>
+      <c r="P44" s="246"/>
       <c r="Q44" s="5"/>
+      <c r="R44" s="246"/>
+      <c r="S44" s="246"/>
+      <c r="T44" s="246"/>
+      <c r="U44" s="246"/>
+      <c r="V44" s="246"/>
+      <c r="W44" s="246"/>
     </row>
     <row r="45" spans="1:23" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A45" s="136" t="inlineStr">
@@ -9641,9 +10933,45 @@
       <c r="O45" s="8"/>
       <c r="P45" s="8"/>
       <c r="Q45" s="9"/>
-    </row>
-    <row r="46" spans="1:23" customHeight="1" ht="6" s="246" customFormat="1"/>
+      <c r="R45" s="246"/>
+      <c r="S45" s="246"/>
+      <c r="T45" s="246"/>
+      <c r="U45" s="246"/>
+      <c r="V45" s="246"/>
+      <c r="W45" s="246"/>
+    </row>
+    <row r="46" spans="1:23" customHeight="1" ht="6" s="246" customFormat="1">
+      <c r="A46" s="246"/>
+      <c r="B46" s="246"/>
+      <c r="C46" s="246"/>
+      <c r="D46" s="246"/>
+      <c r="E46" s="246"/>
+      <c r="F46" s="246"/>
+      <c r="G46" s="246"/>
+      <c r="H46" s="246"/>
+      <c r="I46" s="246"/>
+      <c r="J46" s="246"/>
+      <c r="K46" s="246"/>
+      <c r="L46" s="246"/>
+      <c r="M46" s="246"/>
+      <c r="N46" s="246"/>
+      <c r="O46" s="246"/>
+      <c r="P46" s="246"/>
+      <c r="Q46" s="246"/>
+      <c r="R46" s="246"/>
+      <c r="S46" s="246"/>
+      <c r="T46" s="246"/>
+      <c r="U46" s="246"/>
+      <c r="V46" s="246"/>
+      <c r="W46" s="246"/>
+    </row>
     <row r="47" spans="1:23" customHeight="1" ht="23.25" s="246" customFormat="1">
+      <c r="A47" s="246"/>
+      <c r="B47" s="246"/>
+      <c r="C47" s="246"/>
+      <c r="D47" s="246"/>
+      <c r="E47" s="246"/>
+      <c r="F47" s="246"/>
       <c r="G47" s="163" t="inlineStr">
         <is>
           <r>
@@ -9651,6 +10979,12 @@
           </r>
         </is>
       </c>
+      <c r="H47" s="246"/>
+      <c r="I47" s="246"/>
+      <c r="J47" s="246"/>
+      <c r="K47" s="246"/>
+      <c r="L47" s="246"/>
+      <c r="M47" s="246"/>
       <c r="N47" s="164" t="inlineStr">
         <is>
           <r>
@@ -9658,6 +10992,15 @@
           </r>
         </is>
       </c>
+      <c r="O47" s="246"/>
+      <c r="P47" s="246"/>
+      <c r="Q47" s="246"/>
+      <c r="R47" s="246"/>
+      <c r="S47" s="246"/>
+      <c r="T47" s="246"/>
+      <c r="U47" s="246"/>
+      <c r="V47" s="246"/>
+      <c r="W47" s="246"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -9806,6 +11149,20 @@
           </r>
         </is>
       </c>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
+      <c r="H1" s="246"/>
+      <c r="I1" s="246"/>
+      <c r="J1" s="246"/>
+      <c r="K1" s="246"/>
+      <c r="L1" s="246"/>
+      <c r="M1" s="246"/>
+      <c r="N1" s="246"/>
+      <c r="O1" s="246"/>
     </row>
     <row r="2" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
       <c r="A2" s="201" t="inlineStr">
@@ -9815,6 +11172,20 @@
           </r>
         </is>
       </c>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
+      <c r="D2" s="246"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
+      <c r="H2" s="246"/>
+      <c r="I2" s="246"/>
+      <c r="J2" s="246"/>
+      <c r="K2" s="246"/>
+      <c r="L2" s="246"/>
+      <c r="M2" s="246"/>
+      <c r="N2" s="246"/>
+      <c r="O2" s="246"/>
     </row>
     <row r="3" spans="1:15" customHeight="1" ht="17.25" s="246" customFormat="1">
       <c r="A3" s="201" t="inlineStr">
@@ -9824,6 +11195,20 @@
           </r>
         </is>
       </c>
+      <c r="B3" s="246"/>
+      <c r="C3" s="246"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="246"/>
+      <c r="F3" s="246"/>
+      <c r="G3" s="246"/>
+      <c r="H3" s="246"/>
+      <c r="I3" s="246"/>
+      <c r="J3" s="246"/>
+      <c r="K3" s="246"/>
+      <c r="L3" s="246"/>
+      <c r="M3" s="246"/>
+      <c r="N3" s="246"/>
+      <c r="O3" s="246"/>
     </row>
     <row r="4" spans="1:15" customHeight="1" ht="38.25" s="246" customFormat="1">
       <c r="A4" s="197" t="inlineStr">
@@ -9833,6 +11218,20 @@
           </r>
         </is>
       </c>
+      <c r="B4" s="246"/>
+      <c r="C4" s="246"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="246"/>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
+      <c r="I4" s="246"/>
+      <c r="J4" s="246"/>
+      <c r="K4" s="246"/>
+      <c r="L4" s="246"/>
+      <c r="M4" s="246"/>
+      <c r="N4" s="246"/>
+      <c r="O4" s="246"/>
     </row>
     <row r="5" spans="1:15" customHeight="1" ht="27.75" s="246" customFormat="1">
       <c r="A5" s="204" t="inlineStr">
@@ -9842,6 +11241,20 @@
           </r>
         </is>
       </c>
+      <c r="B5" s="246"/>
+      <c r="C5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="246"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
+      <c r="I5" s="246"/>
+      <c r="J5" s="246"/>
+      <c r="K5" s="246"/>
+      <c r="L5" s="246"/>
+      <c r="M5" s="246"/>
+      <c r="N5" s="246"/>
+      <c r="O5" s="246"/>
     </row>
     <row r="6" spans="1:15" customHeight="1" ht="24.95" s="246" customFormat="1">
       <c r="A6" s="92" t="inlineStr">
@@ -9958,6 +11371,7 @@
       <c r="O8" s="81"/>
     </row>
     <row r="9" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A9" s="246"/>
       <c r="B9" s="305"/>
       <c r="C9" s="181" t="inlineStr">
         <is>
@@ -9980,15 +11394,19 @@
           </r>
         </is>
       </c>
+      <c r="I9" s="246"/>
       <c r="J9" s="305"/>
       <c r="K9" s="203" t="str">
         <f>구매리스트!D7</f>
         <v>0</v>
       </c>
+      <c r="L9" s="246"/>
+      <c r="M9" s="246"/>
       <c r="N9" s="82"/>
       <c r="O9" s="83"/>
     </row>
     <row r="10" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A10" s="246"/>
       <c r="B10" s="305"/>
       <c r="C10" s="202" t="inlineStr">
         <is>
@@ -10023,6 +11441,7 @@
       <c r="O10" s="309"/>
     </row>
     <row r="11" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A11" s="246"/>
       <c r="B11" s="305"/>
       <c r="C11" s="200" t="inlineStr">
         <is>
@@ -10051,6 +11470,7 @@
       <c r="O11" s="313"/>
     </row>
     <row r="12" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A12" s="246"/>
       <c r="B12" s="305"/>
       <c r="C12" s="181" t="inlineStr">
         <is>
@@ -10064,6 +11484,7 @@
         <f>구매리스트!I4</f>
         <v>0</v>
       </c>
+      <c r="F12" s="246"/>
       <c r="G12" s="305"/>
       <c r="H12" s="181" t="inlineStr">
         <is>
@@ -10072,13 +11493,19 @@
           </r>
         </is>
       </c>
+      <c r="I12" s="246"/>
       <c r="J12" s="305"/>
       <c r="K12" s="184" t="str">
         <f>구매리스트!D6</f>
         <v>0</v>
       </c>
+      <c r="L12" s="246"/>
+      <c r="M12" s="246"/>
+      <c r="N12" s="246"/>
+      <c r="O12" s="246"/>
     </row>
     <row r="13" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A13" s="246"/>
       <c r="B13" s="305"/>
       <c r="C13" s="181" t="inlineStr">
         <is>
@@ -10089,6 +11516,7 @@
       </c>
       <c r="D13" s="305"/>
       <c r="E13" s="306"/>
+      <c r="F13" s="246"/>
       <c r="G13" s="305"/>
       <c r="H13" s="181" t="inlineStr">
         <is>
@@ -10097,10 +11525,16 @@
           </r>
         </is>
       </c>
+      <c r="I13" s="246"/>
       <c r="J13" s="305"/>
       <c r="K13" s="306"/>
+      <c r="L13" s="246"/>
+      <c r="M13" s="246"/>
+      <c r="N13" s="246"/>
+      <c r="O13" s="246"/>
     </row>
     <row r="14" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A14" s="246"/>
       <c r="B14" s="305"/>
       <c r="C14" s="179" t="inlineStr">
         <is>
@@ -10136,6 +11570,7 @@
       <c r="O14" s="316"/>
     </row>
     <row r="15" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
+      <c r="A15" s="246"/>
       <c r="B15" s="305"/>
       <c r="C15" s="181" t="inlineStr">
         <is>
@@ -10146,12 +11581,19 @@
       </c>
       <c r="D15" s="305"/>
       <c r="E15" s="306"/>
+      <c r="F15" s="246"/>
       <c r="G15" s="305"/>
       <c r="H15" s="306"/>
+      <c r="I15" s="246"/>
       <c r="J15" s="305"/>
       <c r="K15" s="306"/>
+      <c r="L15" s="246"/>
+      <c r="M15" s="246"/>
+      <c r="N15" s="246"/>
+      <c r="O15" s="246"/>
     </row>
     <row r="16" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
+      <c r="A16" s="246"/>
       <c r="B16" s="305"/>
       <c r="C16" s="180" t="inlineStr">
         <is>
@@ -10174,6 +11616,7 @@
       <c r="O16" s="320"/>
     </row>
     <row r="17" spans="1:15" customHeight="1" ht="21.95" s="246" customFormat="1">
+      <c r="A17" s="246"/>
       <c r="B17" s="305"/>
       <c r="C17" s="181" t="inlineStr">
         <is>
@@ -10187,6 +11630,7 @@
         <f>구매리스트!B6</f>
         <v>0</v>
       </c>
+      <c r="F17" s="246"/>
       <c r="G17" s="305"/>
       <c r="H17" s="181" t="inlineStr">
         <is>
@@ -10195,6 +11639,7 @@
           </r>
         </is>
       </c>
+      <c r="I17" s="246"/>
       <c r="J17" s="305"/>
       <c r="K17" s="210" t="inlineStr">
         <is>
@@ -10203,8 +11648,13 @@
           </r>
         </is>
       </c>
+      <c r="L17" s="246"/>
+      <c r="M17" s="246"/>
+      <c r="N17" s="246"/>
+      <c r="O17" s="246"/>
     </row>
     <row r="18" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
+      <c r="A18" s="246"/>
       <c r="B18" s="305"/>
       <c r="C18" s="181" t="inlineStr">
         <is>
@@ -10215,6 +11665,7 @@
       </c>
       <c r="D18" s="305"/>
       <c r="E18" s="306"/>
+      <c r="F18" s="246"/>
       <c r="G18" s="305"/>
       <c r="H18" s="181" t="inlineStr">
         <is>
@@ -10223,8 +11674,13 @@
           </r>
         </is>
       </c>
+      <c r="I18" s="246"/>
       <c r="J18" s="305"/>
       <c r="K18" s="306"/>
+      <c r="L18" s="246"/>
+      <c r="M18" s="246"/>
+      <c r="N18" s="246"/>
+      <c r="O18" s="246"/>
     </row>
     <row r="19" spans="1:15" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A19" s="253"/>
@@ -10443,6 +11899,8 @@
           </r>
         </is>
       </c>
+      <c r="B26" s="246"/>
+      <c r="C26" s="246"/>
       <c r="D26" s="305"/>
       <c r="E26" s="217" t="inlineStr">
         <is>
@@ -10451,6 +11909,7 @@
           </r>
         </is>
       </c>
+      <c r="F26" s="246"/>
       <c r="G26" s="305"/>
       <c r="H26" s="181" t="inlineStr">
         <is>
@@ -10459,6 +11918,7 @@
           </r>
         </is>
       </c>
+      <c r="I26" s="246"/>
       <c r="J26" s="305"/>
       <c r="K26" s="94" t="inlineStr">
         <is>
@@ -10560,6 +12020,20 @@
           </r>
         </is>
       </c>
+      <c r="B29" s="246"/>
+      <c r="C29" s="246"/>
+      <c r="D29" s="246"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="246"/>
+      <c r="G29" s="246"/>
+      <c r="H29" s="246"/>
+      <c r="I29" s="246"/>
+      <c r="J29" s="246"/>
+      <c r="K29" s="246"/>
+      <c r="L29" s="246"/>
+      <c r="M29" s="246"/>
+      <c r="N29" s="246"/>
+      <c r="O29" s="246"/>
     </row>
     <row r="30" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
       <c r="A30" s="218" t="inlineStr">
@@ -10569,6 +12043,20 @@
           </r>
         </is>
       </c>
+      <c r="B30" s="246"/>
+      <c r="C30" s="246"/>
+      <c r="D30" s="246"/>
+      <c r="E30" s="246"/>
+      <c r="F30" s="246"/>
+      <c r="G30" s="246"/>
+      <c r="H30" s="246"/>
+      <c r="I30" s="246"/>
+      <c r="J30" s="246"/>
+      <c r="K30" s="246"/>
+      <c r="L30" s="246"/>
+      <c r="M30" s="246"/>
+      <c r="N30" s="246"/>
+      <c r="O30" s="246"/>
     </row>
     <row r="31" spans="1:15" customHeight="1" ht="32.25" s="246" customFormat="1">
       <c r="A31" s="218" t="inlineStr">
@@ -10578,6 +12066,20 @@
           </r>
         </is>
       </c>
+      <c r="B31" s="246"/>
+      <c r="C31" s="246"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
+      <c r="G31" s="246"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
+      <c r="L31" s="246"/>
+      <c r="M31" s="246"/>
+      <c r="N31" s="246"/>
+      <c r="O31" s="246"/>
     </row>
     <row r="32" spans="1:15" customHeight="1" ht="9.75" s="246" customFormat="1">
       <c r="A32" s="77"/>
@@ -10622,10 +12124,16 @@
           </r>
         </is>
       </c>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
       <c r="K33" s="219" t="str">
         <f>E24</f>
         <v>0</v>
       </c>
+      <c r="L33" s="246"/>
+      <c r="M33" s="246"/>
+      <c r="N33" s="246"/>
       <c r="O33" s="77"/>
     </row>
     <row r="34" spans="1:15" customHeight="1" ht="85.5" s="246" customFormat="1">
@@ -10653,6 +12161,18 @@
           </r>
         </is>
       </c>
+      <c r="B35" s="246"/>
+      <c r="C35" s="246"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
+      <c r="G35" s="246"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="246"/>
+      <c r="L35" s="246"/>
+      <c r="M35" s="246"/>
       <c r="N35" s="77"/>
       <c r="O35" s="77"/>
     </row>
@@ -10664,6 +12184,18 @@
           </r>
         </is>
       </c>
+      <c r="B36" s="246"/>
+      <c r="C36" s="246"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
+      <c r="G36" s="246"/>
+      <c r="H36" s="246"/>
+      <c r="I36" s="246"/>
+      <c r="J36" s="246"/>
+      <c r="K36" s="246"/>
+      <c r="L36" s="246"/>
+      <c r="M36" s="246"/>
       <c r="N36" s="78"/>
       <c r="O36" s="77"/>
     </row>
@@ -10675,6 +12207,18 @@
           </r>
         </is>
       </c>
+      <c r="B37" s="246"/>
+      <c r="C37" s="246"/>
+      <c r="D37" s="246"/>
+      <c r="E37" s="246"/>
+      <c r="F37" s="246"/>
+      <c r="G37" s="246"/>
+      <c r="H37" s="246"/>
+      <c r="I37" s="246"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246"/>
+      <c r="L37" s="246"/>
+      <c r="M37" s="246"/>
       <c r="N37" s="86"/>
       <c r="O37" s="87"/>
     </row>
@@ -10732,6 +12276,20 @@
           </r>
         </is>
       </c>
+      <c r="B40" s="246"/>
+      <c r="C40" s="246"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="246"/>
+      <c r="G40" s="246"/>
+      <c r="H40" s="246"/>
+      <c r="I40" s="246"/>
+      <c r="J40" s="246"/>
+      <c r="K40" s="246"/>
+      <c r="L40" s="246"/>
+      <c r="M40" s="246"/>
+      <c r="N40" s="246"/>
+      <c r="O40" s="246"/>
     </row>
     <row r="41" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A41" s="192" t="inlineStr">
@@ -10741,6 +12299,20 @@
           </r>
         </is>
       </c>
+      <c r="B41" s="246"/>
+      <c r="C41" s="246"/>
+      <c r="D41" s="246"/>
+      <c r="E41" s="246"/>
+      <c r="F41" s="246"/>
+      <c r="G41" s="246"/>
+      <c r="H41" s="246"/>
+      <c r="I41" s="246"/>
+      <c r="J41" s="246"/>
+      <c r="K41" s="246"/>
+      <c r="L41" s="246"/>
+      <c r="M41" s="246"/>
+      <c r="N41" s="246"/>
+      <c r="O41" s="246"/>
     </row>
     <row r="42" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A42" s="192" t="inlineStr">
@@ -10750,6 +12322,20 @@
           </r>
         </is>
       </c>
+      <c r="B42" s="246"/>
+      <c r="C42" s="246"/>
+      <c r="D42" s="246"/>
+      <c r="E42" s="246"/>
+      <c r="F42" s="246"/>
+      <c r="G42" s="246"/>
+      <c r="H42" s="246"/>
+      <c r="I42" s="246"/>
+      <c r="J42" s="246"/>
+      <c r="K42" s="246"/>
+      <c r="L42" s="246"/>
+      <c r="M42" s="246"/>
+      <c r="N42" s="246"/>
+      <c r="O42" s="246"/>
     </row>
     <row r="43" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
       <c r="A43" s="222" t="inlineStr">
@@ -10827,6 +12413,9 @@
       <c r="I45" s="76"/>
       <c r="J45" s="76"/>
       <c r="K45" s="334"/>
+      <c r="L45" s="246"/>
+      <c r="M45" s="246"/>
+      <c r="N45" s="246"/>
       <c r="O45" s="335"/>
     </row>
     <row r="46" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
@@ -10837,7 +12426,19 @@
           </r>
         </is>
       </c>
+      <c r="B46" s="246"/>
+      <c r="C46" s="246"/>
+      <c r="D46" s="246"/>
+      <c r="E46" s="246"/>
+      <c r="F46" s="246"/>
+      <c r="G46" s="246"/>
+      <c r="H46" s="246"/>
+      <c r="I46" s="246"/>
+      <c r="J46" s="246"/>
       <c r="K46" s="334"/>
+      <c r="L46" s="246"/>
+      <c r="M46" s="246"/>
+      <c r="N46" s="246"/>
       <c r="O46" s="335"/>
     </row>
     <row r="47" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
@@ -10848,7 +12449,19 @@
           </r>
         </is>
       </c>
+      <c r="B47" s="246"/>
+      <c r="C47" s="246"/>
+      <c r="D47" s="246"/>
+      <c r="E47" s="246"/>
+      <c r="F47" s="246"/>
+      <c r="G47" s="246"/>
+      <c r="H47" s="246"/>
+      <c r="I47" s="246"/>
+      <c r="J47" s="246"/>
       <c r="K47" s="334"/>
+      <c r="L47" s="246"/>
+      <c r="M47" s="246"/>
+      <c r="N47" s="246"/>
       <c r="O47" s="335"/>
     </row>
     <row r="48" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
@@ -10859,7 +12472,19 @@
           </r>
         </is>
       </c>
+      <c r="B48" s="246"/>
+      <c r="C48" s="246"/>
+      <c r="D48" s="246"/>
+      <c r="E48" s="246"/>
+      <c r="F48" s="246"/>
+      <c r="G48" s="246"/>
+      <c r="H48" s="246"/>
+      <c r="I48" s="246"/>
+      <c r="J48" s="246"/>
       <c r="K48" s="334"/>
+      <c r="L48" s="246"/>
+      <c r="M48" s="246"/>
+      <c r="N48" s="246"/>
       <c r="O48" s="335"/>
     </row>
     <row r="49" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
@@ -10871,7 +12496,18 @@
         </is>
       </c>
       <c r="B49" s="246"/>
+      <c r="C49" s="246"/>
+      <c r="D49" s="246"/>
+      <c r="E49" s="246"/>
+      <c r="F49" s="246"/>
+      <c r="G49" s="246"/>
+      <c r="H49" s="246"/>
+      <c r="I49" s="246"/>
+      <c r="J49" s="246"/>
       <c r="K49" s="334"/>
+      <c r="L49" s="246"/>
+      <c r="M49" s="246"/>
+      <c r="N49" s="246"/>
       <c r="O49" s="335"/>
     </row>
     <row r="50" spans="1:15" customHeight="1" ht="19.5" s="246" customFormat="1">
@@ -11015,9 +12651,37 @@
           </r>
         </is>
       </c>
+      <c r="B55" s="89"/>
+      <c r="C55" s="89"/>
+      <c r="D55" s="89"/>
+      <c r="E55" s="89"/>
+      <c r="F55" s="89"/>
+      <c r="G55" s="89"/>
+      <c r="H55" s="89"/>
+      <c r="I55" s="89"/>
+      <c r="J55" s="89"/>
+      <c r="K55" s="89"/>
+      <c r="L55" s="89"/>
+      <c r="M55" s="89"/>
+      <c r="N55" s="89"/>
+      <c r="O55" s="89"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56" s="246"/>
+      <c r="B56" s="246"/>
+      <c r="C56" s="246"/>
+      <c r="D56" s="246"/>
+      <c r="E56" s="246"/>
+      <c r="F56" s="246"/>
+      <c r="G56" s="246"/>
+      <c r="H56" s="246"/>
+      <c r="I56" s="246"/>
+      <c r="J56" s="246"/>
+      <c r="K56" s="246"/>
+      <c r="L56" s="246"/>
+      <c r="M56" s="246"/>
+      <c r="N56" s="246"/>
+      <c r="O56" s="246"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -11165,6 +12829,7 @@
       <c r="G1" s="255"/>
       <c r="H1" s="255"/>
       <c r="I1" s="256"/>
+      <c r="J1" s="246"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A2" s="343" t="inlineStr">
@@ -11197,11 +12862,14 @@
         </is>
       </c>
       <c r="I2" s="252"/>
+      <c r="J2" s="246"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A3" s="345" t="s">
         <v>309</v>
       </c>
+      <c r="B3" s="246"/>
+      <c r="C3" s="246"/>
       <c r="D3" s="263"/>
       <c r="E3" s="229" t="inlineStr">
         <is>
@@ -11210,15 +12878,19 @@
           </r>
         </is>
       </c>
+      <c r="F3" s="246"/>
       <c r="G3" s="129" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
       <c r="H3" s="273"/>
       <c r="I3" s="254"/>
+      <c r="J3" s="246"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A4" s="272"/>
+      <c r="B4" s="246"/>
+      <c r="C4" s="246"/>
       <c r="D4" s="263"/>
       <c r="E4" s="346" t="inlineStr">
         <is>
@@ -11227,16 +12899,28 @@
           </r>
         </is>
       </c>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
       <c r="I4" s="263"/>
+      <c r="J4" s="246"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A5" s="272"/>
+      <c r="B5" s="246"/>
+      <c r="C5" s="246"/>
       <c r="D5" s="263"/>
       <c r="E5" s="272"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
       <c r="I5" s="263"/>
+      <c r="J5" s="246"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A6" s="272"/>
+      <c r="B6" s="246"/>
+      <c r="C6" s="246"/>
       <c r="D6" s="263"/>
       <c r="E6" s="347" t="inlineStr">
         <is>
@@ -11245,7 +12929,11 @@
           </r>
         </is>
       </c>
+      <c r="F6" s="246"/>
+      <c r="G6" s="246"/>
+      <c r="H6" s="246"/>
       <c r="I6" s="263"/>
+      <c r="J6" s="246"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A7" s="273"/>
@@ -11259,7 +12947,11 @@
           </r>
         </is>
       </c>
+      <c r="F7" s="246"/>
+      <c r="G7" s="246"/>
+      <c r="H7" s="246"/>
       <c r="I7" s="263"/>
+      <c r="J7" s="246"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A8" s="343" t="inlineStr">
@@ -11283,12 +12975,15 @@
       <c r="G8" s="253"/>
       <c r="H8" s="253"/>
       <c r="I8" s="254"/>
+      <c r="J8" s="246"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
       <c r="A9" s="349" t="str">
         <f>구매리스트!B14</f>
         <v>0</v>
       </c>
+      <c r="B9" s="246"/>
+      <c r="C9" s="246"/>
       <c r="D9" s="263"/>
       <c r="E9" s="235" t="inlineStr">
         <is>
@@ -11311,6 +13006,8 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A10" s="272"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
       <c r="D10" s="263"/>
       <c r="E10" s="226" t="inlineStr">
         <is>
@@ -11323,6 +13020,7 @@
       <c r="G10" s="251"/>
       <c r="H10" s="251"/>
       <c r="I10" s="252"/>
+      <c r="J10" s="246"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="35.25" s="246" customFormat="1">
       <c r="A11" s="273"/>
@@ -11333,10 +13031,14 @@
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
       <c r="I11" s="53" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
+      <c r="J11" s="246"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A12" s="343" t="inlineStr">
@@ -11360,6 +13062,7 @@
       <c r="G12" s="251"/>
       <c r="H12" s="251"/>
       <c r="I12" s="252"/>
+      <c r="J12" s="246"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A13" s="350" t="inlineStr">
@@ -11369,6 +13072,8 @@
           </r>
         </is>
       </c>
+      <c r="B13" s="246"/>
+      <c r="C13" s="246"/>
       <c r="D13" s="263"/>
       <c r="E13" s="230" t="inlineStr">
         <is>
@@ -11377,7 +13082,11 @@
           </r>
         </is>
       </c>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
       <c r="I13" s="263"/>
+      <c r="J13" s="246"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="9.75" s="246" customFormat="1">
       <c r="A14" s="273"/>
@@ -11389,6 +13098,7 @@
       <c r="G14" s="253"/>
       <c r="H14" s="253"/>
       <c r="I14" s="254"/>
+      <c r="J14" s="246"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
       <c r="A15" s="343" t="inlineStr">
@@ -11418,6 +13128,7 @@
       <c r="G15" s="251"/>
       <c r="H15" s="251"/>
       <c r="I15" s="252"/>
+      <c r="J15" s="246"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A16" s="232" t="str">
@@ -11437,7 +13148,11 @@
           </r>
         </is>
       </c>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
       <c r="I16" s="263"/>
+      <c r="J16" s="246"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
       <c r="A17" s="343" t="inlineStr">
@@ -11464,6 +13179,7 @@
       <c r="G17" s="251"/>
       <c r="H17" s="251"/>
       <c r="I17" s="252"/>
+      <c r="J17" s="246"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A18" s="351" t="str">
@@ -11481,6 +13197,7 @@
       <c r="G18" s="253"/>
       <c r="H18" s="253"/>
       <c r="I18" s="254"/>
+      <c r="J18" s="246"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
@@ -11528,6 +13245,7 @@
           </r>
         </is>
       </c>
+      <c r="J19" s="246"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="10.5" s="246" customFormat="1">
       <c r="A20" s="30"/>
@@ -11539,6 +13257,7 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
+      <c r="J20" s="246"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
@@ -11984,7 +13703,9 @@
           </r>
         </is>
       </c>
+      <c r="F33" s="246"/>
       <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -12006,7 +13727,11 @@
           </r>
         </is>
       </c>
+      <c r="F34" s="246"/>
+      <c r="G34" s="246"/>
+      <c r="H34" s="246"/>
       <c r="I34" s="32"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="30" t="inlineStr">
@@ -12024,6 +13749,7 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="32"/>
+      <c r="J35"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="30"/>
@@ -12035,6 +13761,7 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="32"/>
+      <c r="J36"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="30"/>
@@ -12046,6 +13773,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="32"/>
+      <c r="J37"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="30"/>
@@ -12057,6 +13785,7 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32"/>
+      <c r="J38"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="30"/>
@@ -12068,6 +13797,7 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="32"/>
+      <c r="J39"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
@@ -12079,6 +13809,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
       <c r="I40" s="35"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -12183,6 +13914,7 @@
       <c r="G1" s="255"/>
       <c r="H1" s="255"/>
       <c r="I1" s="256"/>
+      <c r="J1" s="246"/>
     </row>
     <row r="2" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A2" s="343" t="inlineStr">
@@ -12215,11 +13947,14 @@
         </is>
       </c>
       <c r="I2" s="252"/>
+      <c r="J2" s="246"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A3" s="345" t="s">
         <v>309</v>
       </c>
+      <c r="B3" s="246"/>
+      <c r="C3" s="246"/>
       <c r="D3" s="263"/>
       <c r="E3" s="229" t="inlineStr">
         <is>
@@ -12228,15 +13963,19 @@
           </r>
         </is>
       </c>
+      <c r="F3" s="246"/>
       <c r="G3" s="129" t="str">
         <f>차량인보이스!G3</f>
         <v>0</v>
       </c>
       <c r="H3" s="273"/>
       <c r="I3" s="254"/>
+      <c r="J3" s="246"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A4" s="272"/>
+      <c r="B4" s="246"/>
+      <c r="C4" s="246"/>
       <c r="D4" s="263"/>
       <c r="E4" s="346" t="inlineStr">
         <is>
@@ -12245,16 +13984,28 @@
           </r>
         </is>
       </c>
+      <c r="F4" s="246"/>
+      <c r="G4" s="246"/>
+      <c r="H4" s="246"/>
       <c r="I4" s="263"/>
+      <c r="J4" s="246"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A5" s="272"/>
+      <c r="B5" s="246"/>
+      <c r="C5" s="246"/>
       <c r="D5" s="263"/>
       <c r="E5" s="272"/>
+      <c r="F5" s="246"/>
+      <c r="G5" s="246"/>
+      <c r="H5" s="246"/>
       <c r="I5" s="263"/>
+      <c r="J5" s="246"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A6" s="272"/>
+      <c r="B6" s="246"/>
+      <c r="C6" s="246"/>
       <c r="D6" s="263"/>
       <c r="E6" s="347" t="inlineStr">
         <is>
@@ -12263,7 +14014,11 @@
           </r>
         </is>
       </c>
+      <c r="F6" s="246"/>
+      <c r="G6" s="246"/>
+      <c r="H6" s="246"/>
       <c r="I6" s="263"/>
+      <c r="J6" s="246"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A7" s="273"/>
@@ -12277,7 +14032,11 @@
           </r>
         </is>
       </c>
+      <c r="F7" s="246"/>
+      <c r="G7" s="246"/>
+      <c r="H7" s="246"/>
       <c r="I7" s="263"/>
+      <c r="J7" s="246"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A8" s="343" t="inlineStr">
@@ -12301,12 +14060,15 @@
       <c r="G8" s="253"/>
       <c r="H8" s="253"/>
       <c r="I8" s="254"/>
+      <c r="J8" s="246"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="65.25" s="246" customFormat="1">
       <c r="A9" s="372" t="str">
         <f>차량인보이스!A9</f>
         <v>0</v>
       </c>
+      <c r="B9" s="246"/>
+      <c r="C9" s="246"/>
       <c r="D9" s="263"/>
       <c r="E9" s="235" t="inlineStr">
         <is>
@@ -12329,6 +14091,8 @@
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A10" s="272"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
       <c r="D10" s="263"/>
       <c r="E10" s="226" t="inlineStr">
         <is>
@@ -12341,6 +14105,7 @@
       <c r="G10" s="251"/>
       <c r="H10" s="251"/>
       <c r="I10" s="252"/>
+      <c r="J10" s="246"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="35.25" s="246" customFormat="1">
       <c r="A11" s="273"/>
@@ -12351,10 +14116,14 @@
         <f>구매리스트!B3</f>
         <v>0</v>
       </c>
+      <c r="F11" s="246"/>
+      <c r="G11" s="246"/>
+      <c r="H11" s="246"/>
       <c r="I11" s="53" t="str">
         <f>TODAY()</f>
         <v>0</v>
       </c>
+      <c r="J11" s="246"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A12" s="343" t="inlineStr">
@@ -12378,6 +14147,7 @@
       <c r="G12" s="251"/>
       <c r="H12" s="251"/>
       <c r="I12" s="252"/>
+      <c r="J12" s="246"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A13" s="350" t="inlineStr">
@@ -12387,6 +14157,8 @@
           </r>
         </is>
       </c>
+      <c r="B13" s="246"/>
+      <c r="C13" s="246"/>
       <c r="D13" s="263"/>
       <c r="E13" s="230" t="inlineStr">
         <is>
@@ -12395,7 +14167,11 @@
           </r>
         </is>
       </c>
+      <c r="F13" s="246"/>
+      <c r="G13" s="246"/>
+      <c r="H13" s="246"/>
       <c r="I13" s="263"/>
+      <c r="J13" s="246"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="9.75" s="246" customFormat="1">
       <c r="A14" s="273"/>
@@ -12407,6 +14183,7 @@
       <c r="G14" s="253"/>
       <c r="H14" s="253"/>
       <c r="I14" s="254"/>
+      <c r="J14" s="246"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
       <c r="A15" s="343" t="inlineStr">
@@ -12436,6 +14213,7 @@
       <c r="G15" s="251"/>
       <c r="H15" s="251"/>
       <c r="I15" s="252"/>
+      <c r="J15" s="246"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A16" s="232" t="str">
@@ -12455,7 +14233,11 @@
           </r>
         </is>
       </c>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
       <c r="I16" s="263"/>
+      <c r="J16" s="246"/>
     </row>
     <row r="17" spans="1:10" customHeight="1" ht="16.5" s="246" customFormat="1">
       <c r="A17" s="343" t="inlineStr">
@@ -12482,6 +14264,7 @@
       <c r="G17" s="251"/>
       <c r="H17" s="251"/>
       <c r="I17" s="252"/>
+      <c r="J17" s="246"/>
     </row>
     <row r="18" spans="1:10" customHeight="1" ht="24" s="246" customFormat="1">
       <c r="A18" s="351" t="str">
@@ -12499,6 +14282,7 @@
       <c r="G18" s="253"/>
       <c r="H18" s="253"/>
       <c r="I18" s="254"/>
+      <c r="J18" s="246"/>
     </row>
     <row r="19" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
       <c r="A19" s="22" t="inlineStr">
@@ -12546,6 +14330,7 @@
           </r>
         </is>
       </c>
+      <c r="J19" s="246"/>
     </row>
     <row r="20" spans="1:10" customHeight="1" ht="10.5" s="246" customFormat="1">
       <c r="A20" s="30"/>
@@ -12557,6 +14342,7 @@
       <c r="G20" s="31"/>
       <c r="H20" s="31"/>
       <c r="I20" s="32"/>
+      <c r="J20" s="246"/>
     </row>
     <row r="21" spans="1:10" customHeight="1" ht="27" s="246" customFormat="1">
       <c r="A21" s="36" t="inlineStr">
@@ -13025,7 +14811,9 @@
           </r>
         </is>
       </c>
+      <c r="F33" s="246"/>
       <c r="G33" s="246"/>
+      <c r="H33" s="246"/>
       <c r="I33" s="29"/>
       <c r="J33" s="18"/>
     </row>
@@ -13047,7 +14835,11 @@
           </r>
         </is>
       </c>
+      <c r="F34" s="246"/>
+      <c r="G34" s="246"/>
+      <c r="H34" s="246"/>
       <c r="I34" s="32"/>
+      <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="30" t="inlineStr">
@@ -13065,6 +14857,7 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="32"/>
+      <c r="J35"/>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="30"/>
@@ -13076,6 +14869,7 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="32"/>
+      <c r="J36"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="30"/>
@@ -13087,6 +14881,7 @@
       <c r="G37" s="31"/>
       <c r="H37" s="31"/>
       <c r="I37" s="32"/>
+      <c r="J37"/>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="30"/>
@@ -13098,6 +14893,7 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="32"/>
+      <c r="J38"/>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="30"/>
@@ -13109,6 +14905,7 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="32"/>
+      <c r="J39"/>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="33"/>
@@ -13120,6 +14917,7 @@
       <c r="G40" s="34"/>
       <c r="H40" s="34"/>
       <c r="I40" s="35"/>
+      <c r="J40"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -13207,23 +15005,34 @@
   <sheetData>
     <row r="1" spans="1:7" customHeight="1" ht="84" s="246" customFormat="1">
       <c r="A1" s="243"/>
+      <c r="B1" s="246"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
       <c r="E1" s="242" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">PROFORM INVOICE</t>
-          </r>
-        </is>
-      </c>
+            <t xml:space="preserve">PROFORMA INVOICE</t>
+          </r>
+        </is>
+      </c>
+      <c r="F1" s="246"/>
+      <c r="G1" s="246"/>
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="246" customFormat="1">
       <c r="A2" s="244" t="s">
         <v>348</v>
       </c>
+      <c r="B2" s="246"/>
+      <c r="C2" s="246"/>
       <c r="D2" s="244"/>
+      <c r="E2" s="246"/>
+      <c r="F2" s="246"/>
+      <c r="G2" s="246"/>
     </row>
     <row r="3" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
+      <c r="A3" s="246"/>
+      <c r="B3" s="246"/>
+      <c r="C3" s="246"/>
       <c r="D3" s="244"/>
       <c r="E3" s="44" t="inlineStr">
         <is>
@@ -13259,6 +15068,8 @@
     <row r="5" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A5" s="239"/>
       <c r="B5" s="239"/>
+      <c r="C5" s="246"/>
+      <c r="D5" s="246"/>
       <c r="E5" s="44" t="inlineStr">
         <is>
           <r>
@@ -13275,6 +15086,8 @@
     <row r="6" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A6" s="239"/>
       <c r="B6" s="239"/>
+      <c r="C6" s="246"/>
+      <c r="D6" s="246"/>
       <c r="E6" s="44" t="inlineStr">
         <is>
           <r>
@@ -13287,10 +15100,13 @@
     </row>
     <row r="7" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A7" s="239"/>
+      <c r="B7" s="246"/>
+      <c r="C7" s="246"/>
+      <c r="D7" s="246"/>
       <c r="E7" s="44" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Adress</t>
+            <t xml:space="preserve">Address</t>
           </r>
         </is>
       </c>
@@ -13299,6 +15115,9 @@
     </row>
     <row r="8" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A8" s="239"/>
+      <c r="B8" s="246"/>
+      <c r="C8" s="246"/>
+      <c r="D8" s="246"/>
       <c r="E8" s="44" t="inlineStr">
         <is>
           <r>
@@ -13312,6 +15131,8 @@
     <row r="9" spans="1:7" customHeight="1" ht="24.75" s="246" customFormat="1">
       <c r="A9" s="239"/>
       <c r="B9" s="239"/>
+      <c r="C9" s="246"/>
+      <c r="D9" s="246"/>
       <c r="E9" s="44" t="inlineStr">
         <is>
           <r>
@@ -13324,6 +15145,9 @@
     </row>
     <row r="10" spans="1:7" customHeight="1" ht="18" s="246" customFormat="1">
       <c r="A10" s="239"/>
+      <c r="B10" s="246"/>
+      <c r="C10" s="246"/>
+      <c r="D10" s="246"/>
       <c r="E10" s="44"/>
       <c r="F10" s="46"/>
       <c r="G10" s="45"/>
@@ -13331,6 +15155,8 @@
     <row r="11" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A11" s="238"/>
       <c r="B11" s="238"/>
+      <c r="C11" s="246"/>
+      <c r="D11" s="246"/>
       <c r="E11" s="44" t="inlineStr">
         <is>
           <r>
@@ -13346,6 +15172,9 @@
     </row>
     <row r="12" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A12" s="238"/>
+      <c r="B12" s="246"/>
+      <c r="C12" s="246"/>
+      <c r="D12" s="246"/>
       <c r="E12" s="44" t="inlineStr">
         <is>
           <r>
@@ -13361,6 +15190,7 @@
     </row>
     <row r="13" spans="1:7" customHeight="1" ht="23.25" s="246" customFormat="1">
       <c r="A13" s="245"/>
+      <c r="B13" s="246"/>
       <c r="C13" s="51"/>
       <c r="D13" s="51"/>
       <c r="E13" s="44" t="inlineStr">
@@ -13378,9 +15208,12 @@
     </row>
     <row r="14" spans="1:7" customHeight="1" ht="17.25" s="246" customFormat="1">
       <c r="A14" s="245"/>
+      <c r="B14" s="246"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="381"/>
+      <c r="F14" s="246"/>
+      <c r="G14" s="246"/>
     </row>
     <row r="15" spans="1:7" customHeight="1" ht="26.25" s="246" customFormat="1">
       <c r="A15" s="382" t="inlineStr">
@@ -13426,7 +15259,7 @@
       <c r="A17" s="240" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Swift Cose</t>
+            <t xml:space="preserve">Swift Code</t>
           </r>
         </is>
       </c>
@@ -13438,7 +15271,7 @@
       <c r="E17" s="240" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Bank Adress</t>
+            <t xml:space="preserve">Bank Address</t>
           </r>
         </is>
       </c>
@@ -13463,7 +15296,7 @@
       <c r="E18" s="240" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beneficiary Adress</t>
+            <t xml:space="preserve">Beneficiary Address</t>
           </r>
         </is>
       </c>
@@ -13473,9 +15306,13 @@
       <c r="G18" s="384"/>
     </row>
     <row r="19" spans="1:7">
+      <c r="A19" s="246"/>
+      <c r="B19" s="246"/>
       <c r="C19" s="43"/>
       <c r="D19" s="43"/>
       <c r="E19" s="381"/>
+      <c r="F19" s="246"/>
+      <c r="G19" s="246"/>
     </row>
     <row r="20" spans="1:7" customHeight="1" ht="25.5" s="246" customFormat="1">
       <c r="A20" s="42" t="inlineStr">

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="376">
   <si>
     <r>
       <t xml:space="preserve">말소증</t>
@@ -488,11 +488,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">자가용</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">④ 차               명</t>
     </r>
   </si>
@@ -912,11 +907,6 @@
   <si>
     <r>
       <t xml:space="preserve">③Usage</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Private car</t>
     </r>
   </si>
   <si>
@@ -7263,12 +7253,9 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="152" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">자가용</t>
-          </r>
-        </is>
+      <c r="P4" s="152" t="str">
+        <f>구매리스트!B8</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="255"/>
       <c r="R4" s="245"/>
@@ -7370,7 +7357,7 @@
       <c r="C7" s="254"/>
       <c r="D7" s="255"/>
       <c r="E7" s="257" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F7" s="254"/>
       <c r="G7" s="254"/>
@@ -7406,7 +7393,7 @@
       </c>
       <c r="D8" s="254"/>
       <c r="E8" s="259" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F8" s="254"/>
       <c r="G8" s="254"/>
@@ -9205,12 +9192,9 @@
           </r>
         </is>
       </c>
-      <c r="P4" s="178" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Private car</t>
-          </r>
-        </is>
+      <c r="P4" s="178" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(구매리스트!B8,"자가용","Private"),"영업용","Business"),"관용","Official")</f>
+        <v>0</v>
       </c>
       <c r="Q4" s="255"/>
       <c r="R4" s="245"/>
@@ -9333,7 +9317,7 @@
       <c r="C7" s="254"/>
       <c r="D7" s="255"/>
       <c r="E7" s="257" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F7" s="254"/>
       <c r="G7" s="254"/>
@@ -9372,7 +9356,7 @@
       </c>
       <c r="D8" s="254"/>
       <c r="E8" s="259" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F8" s="254"/>
       <c r="G8" s="254"/>
@@ -11752,7 +11736,7 @@
       </c>
       <c r="D21" s="303"/>
       <c r="E21" s="392" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F21" s="250"/>
       <c r="G21" s="303"/>
@@ -12872,7 +12856,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A3" s="344" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B3" s="245"/>
       <c r="C3" s="245"/>
@@ -13957,7 +13941,7 @@
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="18" s="245" customFormat="1">
       <c r="A3" s="344" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B3" s="245"/>
       <c r="C3" s="245"/>
@@ -15026,7 +15010,7 @@
     </row>
     <row r="2" spans="1:7" customHeight="1" ht="11.25" s="245" customFormat="1">
       <c r="A2" s="243" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B2" s="245"/>
       <c r="C2" s="245"/>
@@ -15246,7 +15230,7 @@
       </c>
       <c r="B16" s="383"/>
       <c r="C16" s="384" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="D16" s="383"/>
       <c r="E16" s="239" t="inlineStr">
@@ -15257,7 +15241,7 @@
         </is>
       </c>
       <c r="F16" s="385" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G16" s="383"/>
     </row>
@@ -15271,7 +15255,7 @@
       </c>
       <c r="B17" s="383"/>
       <c r="C17" s="384" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D17" s="383"/>
       <c r="E17" s="239" t="inlineStr">
@@ -15282,7 +15266,7 @@
         </is>
       </c>
       <c r="F17" s="240" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G17" s="383"/>
     </row>
@@ -15296,7 +15280,7 @@
       </c>
       <c r="B18" s="383"/>
       <c r="C18" s="384" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D18" s="383"/>
       <c r="E18" s="239" t="inlineStr">
@@ -15307,7 +15291,7 @@
         </is>
       </c>
       <c r="F18" s="386" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G18" s="383"/>
     </row>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="3" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
+    <workbookView activeTab="4" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="800" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="구매리스트" sheetId="1" r:id="rId4"/>
@@ -3445,7 +3445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="398">
+  <cellXfs count="400">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
@@ -4639,6 +4639,12 @@
     </xf>
     <xf xfId="0" fontId="0" numFmtId="0" fillId="13" borderId="17" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="11" borderId="24" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
+    </xf>
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="11" borderId="2" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" shrinkToFit="true" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12798,7 +12804,7 @@
     <col min="4" max="4" width="23.625" customWidth="true" style="245"/>
     <col min="5" max="5" width="7.75" customWidth="true" style="245"/>
     <col min="6" max="6" width="2.125" customWidth="true" style="245"/>
-    <col min="7" max="7" width="12.25" customWidth="true" style="245"/>
+    <col min="7" max="7" width="19.5" customWidth="true" style="245"/>
     <col min="8" max="8" width="13.75" customWidth="true" style="245"/>
     <col min="9" max="9" width="13.25" customWidth="true" style="245"/>
   </cols>
@@ -12840,7 +12846,7 @@
         </is>
       </c>
       <c r="F2" s="250"/>
-      <c r="G2" s="128" t="str">
+      <c r="G2" s="398" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>
@@ -12869,7 +12875,7 @@
         </is>
       </c>
       <c r="F3" s="245"/>
-      <c r="G3" s="129" t="str">
+      <c r="G3" s="399" t="str">
         <f>구매리스트!B12</f>
         <v>0</v>
       </c>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -534,9 +534,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">120111-0922270</t>
-    </r>
+    <t>120111-1058941</t>
   </si>
   <si>
     <r>
@@ -5757,10 +5755,7 @@
           </r>
         </is>
       </c>
-      <c r="I6" s="115" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G6,"승용 소형","Small Passenger"),"승용 중형","Medium Passenger"),"승용 대형","HEAVY Passenger"),"중형 승합","Medium Ven"),"대형 승합","Large Ven"),"중형 화물","Medium Cargo")</f>
-        <v>0</v>
-      </c>
+      <c r="I6" s="115"/>
       <c r="J6" s="243"/>
       <c r="K6" s="243"/>
       <c r="L6" s="243"/>
@@ -7405,12 +7400,8 @@
       </c>
       <c r="K8" s="252"/>
       <c r="L8" s="253"/>
-      <c r="M8" s="257" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">120111-0922270</t>
-          </r>
-        </is>
+      <c r="M8" s="257" t="s">
+        <v>101</v>
       </c>
       <c r="N8" s="252"/>
       <c r="O8" s="252"/>
@@ -9367,12 +9358,8 @@
       </c>
       <c r="K8" s="252"/>
       <c r="L8" s="253"/>
-      <c r="M8" s="257" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">120111-0922270</t>
-          </r>
-        </is>
+      <c r="M8" s="257" t="s">
+        <v>101</v>
       </c>
       <c r="N8" s="252"/>
       <c r="O8" s="252"/>
@@ -11745,12 +11732,8 @@
       </c>
       <c r="I21" s="248"/>
       <c r="J21" s="301"/>
-      <c r="K21" s="320" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">120111-0922270</t>
-          </r>
-        </is>
+      <c r="K21" s="320" t="s">
+        <v>101</v>
       </c>
       <c r="L21" s="248"/>
       <c r="M21" s="248"/>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -6093,10 +6093,7 @@
         </is>
       </c>
       <c r="H13" s="244"/>
-      <c r="I13" s="113" t="str">
-        <f>SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(G13,"휘발유","GASOLINE"),"경유","DIESEL"),"LPG","LPG"),"하이브리드","HYBRID")</f>
-        <v>0</v>
-      </c>
+      <c r="I13" s="113"/>
       <c r="J13" s="243"/>
       <c r="K13" s="243"/>
       <c r="L13" s="243"/>

--- a/resources/templates/karaba/clearance_set.xlsx
+++ b/resources/templates/karaba/clearance_set.xlsx
@@ -1740,9 +1740,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Fax No          : 82- 505 - 366 - 9977</t>
-    </r>
+    <t>Fax No          : 82- 32 - 710 - 1881</t>
   </si>
   <si>
     <r>
@@ -13692,12 +13690,8 @@
       <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Fax No          : 82- 505 - 366 - 9977</t>
-          </r>
-        </is>
+      <c r="A35" s="30" t="s">
+        <v>341</v>
       </c>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
@@ -14792,12 +14786,8 @@
       <c r="J34"/>
     </row>
     <row r="35" spans="1:10">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">Fax No          : 82- 505 - 366 - 9977</t>
-          </r>
-        </is>
+      <c r="A35" s="30" t="s">
+        <v>341</v>
       </c>
       <c r="B35" s="31"/>
       <c r="C35" s="31"/>
